--- a/VT LTT Project/Data/Project Database Files/eDCU/48V HighCurrent/Configuration Files/Limit Files/6Head/FE_FF_Frame_Limit_eDCU_Thermal_Endurance_v6.xlsx
+++ b/VT LTT Project/Data/Project Database Files/eDCU/48V HighCurrent/Configuration Files/Limit Files/6Head/FE_FF_Frame_Limit_eDCU_Thermal_Endurance_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eDCU LTT\VT LTT Project\Data\Project Database Files\eDCU\48V HighCurrent\Configuration Files\Limit Files\6Head\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBEC59F-9C87-42A0-AD43-198D7F6CBECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66093EB-2715-4079-AD5A-7CD67E4BA0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{49D2488A-EB0E-4C68-8F67-50F12E4C4F72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{49D2488A-EB0E-4C68-8F67-50F12E4C4F72}"/>
   </bookViews>
   <sheets>
     <sheet name="Change List" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="360">
   <si>
     <t>ID</t>
   </si>
@@ -1126,6 +1126,12 @@
   </si>
   <si>
     <t>Mode 14</t>
+  </si>
+  <si>
+    <t>24.02.2026</t>
+  </si>
+  <si>
+    <t>Update the file for High Current eDCU for Mode 11,12 after trial for Endurance test, to start TVS reliability test</t>
   </si>
 </sst>
 </file>
@@ -2494,6 +2500,9 @@
     <xf numFmtId="0" fontId="0" fillId="43" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2531,9 +2540,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="42" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3354,11 +3360,19 @@
         <v>346</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="69"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="77"/>
+    <row r="8" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="69">
+        <v>6</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" s="77" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="69"/>
@@ -5108,26 +5122,26 @@
         <v>2.66</v>
       </c>
       <c r="AK15" s="20">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AL15" s="19">
         <f>($AK$15*5/Misc!$L$22)-0.1</f>
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AM15" s="19">
         <f>($AK$15*5/Misc!$L$22)+0.1</f>
-        <v>2.66</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AN15" s="20">
-        <v>2.5499999999999998</v>
+        <v>2.35</v>
       </c>
       <c r="AO15" s="19">
         <f>(AN15*5/Misc!$L$19)-0.1</f>
-        <v>2.4499999999999997</v>
+        <v>2.25</v>
       </c>
       <c r="AP15" s="19">
         <f>(AN15*5/Misc!$L$19)+0.1</f>
-        <v>2.65</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AQ15" s="20">
         <v>2.5499999999999998</v>
@@ -5314,26 +5328,26 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="AK16" s="20">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" s="19">
         <f>($AK$16*5/Misc!$L$22)-0.1</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AM16" s="19">
         <f>($AK$16*5/Misc!$L$22)+0.1</f>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="AN16" s="20">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AO16" s="19">
         <f>(AN16*5/Misc!$L$19)-0.1</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AP16" s="19">
         <f>(AN16*5/Misc!$L$19)+0.1</f>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16" s="20">
         <v>2.7</v>
@@ -6541,16 +6555,16 @@
         <f>($AH$24*5/Misc!$L$21)+0.015</f>
         <v>2.5020000000000002</v>
       </c>
-      <c r="AK24" s="21">
-        <v>2.4870000000000001</v>
+      <c r="AK24" s="20">
+        <v>2.4900000000000002</v>
       </c>
       <c r="AL24" s="19">
         <f>($AK$24*5/Misc!$L$22)-0.015</f>
-        <v>2.472</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="AM24" s="19">
         <f>($AK$24*5/Misc!$L$22)+0.015</f>
-        <v>2.5020000000000002</v>
+        <v>2.5050000000000003</v>
       </c>
       <c r="AN24" s="20">
         <v>2.4900000000000002</v>
@@ -6744,16 +6758,16 @@
         <f>($AH$25*5/Misc!$L$21)+0.015</f>
         <v>2.5050000000000003</v>
       </c>
-      <c r="AK25" s="21">
-        <v>2.4900000000000002</v>
+      <c r="AK25" s="20">
+        <v>2.4950000000000001</v>
       </c>
       <c r="AL25" s="19">
         <f>($AK$25*5/Misc!$L$22)-0.015</f>
-        <v>2.4750000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="AM25" s="19">
         <f>($AK$25*5/Misc!$L$22)+0.015</f>
-        <v>2.5050000000000003</v>
+        <v>2.5100000000000002</v>
       </c>
       <c r="AN25" s="20">
         <v>2.4950000000000001</v>
@@ -8322,7 +8336,7 @@
       </c>
       <c r="I36" s="19">
         <f>Misc!$K$12*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="J36" s="20"/>
       <c r="K36" s="19">
@@ -8331,7 +8345,7 @@
       </c>
       <c r="L36" s="19">
         <f>Misc!$K$13*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="M36" s="20"/>
       <c r="N36" s="19">
@@ -8340,7 +8354,7 @@
       </c>
       <c r="O36" s="19">
         <f>Misc!$K$14*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="P36" s="20"/>
       <c r="Q36" s="19">
@@ -8349,7 +8363,7 @@
       </c>
       <c r="R36" s="19">
         <f>Misc!$K$15*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="S36" s="20"/>
       <c r="T36" s="19">
@@ -8358,7 +8372,7 @@
       </c>
       <c r="U36" s="19">
         <f>Misc!$K$16*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="V36" s="20"/>
       <c r="W36" s="19">
@@ -8367,7 +8381,7 @@
       </c>
       <c r="X36" s="19">
         <f>Misc!$K$17*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="Y36" s="20"/>
       <c r="Z36" s="19">
@@ -8376,7 +8390,7 @@
       </c>
       <c r="AA36" s="19">
         <f>Misc!$K$18*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AB36" s="20"/>
       <c r="AC36" s="19">
@@ -8385,7 +8399,7 @@
       </c>
       <c r="AD36" s="19">
         <f>Misc!$K$19*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AE36" s="20"/>
       <c r="AF36" s="19">
@@ -8394,7 +8408,7 @@
       </c>
       <c r="AG36" s="19">
         <f>Misc!$K$20*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AH36" s="21"/>
       <c r="AI36" s="19">
@@ -8403,7 +8417,7 @@
       </c>
       <c r="AJ36" s="19">
         <f>Misc!$K$21*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AK36" s="21"/>
       <c r="AL36" s="19">
@@ -8412,34 +8426,33 @@
       </c>
       <c r="AM36" s="19">
         <f>Misc!$K$22*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AN36" s="20"/>
       <c r="AO36" s="19">
-        <f>Misc!A35*1.05</f>
-        <v>0</v>
+        <f>Misc!J23*1.05</f>
+        <v>-21</v>
       </c>
       <c r="AP36" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AQ36" s="20"/>
       <c r="AR36" s="19">
-        <f>Misc!D35*1.05</f>
+        <f>Misc!D34*1.05</f>
         <v>0</v>
       </c>
       <c r="AS36" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AT36" s="20"/>
       <c r="AU36" s="19">
-        <f>Misc!G35*1.05</f>
-        <v>115.5</v>
+        <v>0</v>
       </c>
       <c r="AV36" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AW36" s="20"/>
       <c r="AX36" s="19">
@@ -8448,7 +8461,7 @@
       </c>
       <c r="AY36" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AZ36" s="20"/>
       <c r="BA36" s="19">
@@ -8457,7 +8470,7 @@
       </c>
       <c r="BB36" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="BC36" s="20"/>
       <c r="BD36" s="19">
@@ -8466,7 +8479,7 @@
       </c>
       <c r="BE36" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="37" spans="1:60" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -8491,7 +8504,7 @@
       </c>
       <c r="I37" s="19">
         <f>Misc!$K$12*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="J37" s="20"/>
       <c r="K37" s="19">
@@ -8500,7 +8513,7 @@
       </c>
       <c r="L37" s="19">
         <f>Misc!$K$13*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="M37" s="20"/>
       <c r="N37" s="19">
@@ -8509,7 +8522,7 @@
       </c>
       <c r="O37" s="19">
         <f>Misc!$K$14*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="P37" s="20"/>
       <c r="Q37" s="19">
@@ -8518,7 +8531,7 @@
       </c>
       <c r="R37" s="19">
         <f>Misc!$K$15*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="S37" s="20"/>
       <c r="T37" s="19">
@@ -8527,7 +8540,7 @@
       </c>
       <c r="U37" s="19">
         <f>Misc!$K$16*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="V37" s="20"/>
       <c r="W37" s="19">
@@ -8536,7 +8549,7 @@
       </c>
       <c r="X37" s="19">
         <f>Misc!$K$17*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="Y37" s="20"/>
       <c r="Z37" s="19">
@@ -8545,7 +8558,7 @@
       </c>
       <c r="AA37" s="19">
         <f>Misc!$K$18*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AB37" s="20"/>
       <c r="AC37" s="19">
@@ -8554,7 +8567,7 @@
       </c>
       <c r="AD37" s="19">
         <f>Misc!$K$19*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AE37" s="20"/>
       <c r="AF37" s="19">
@@ -8563,7 +8576,7 @@
       </c>
       <c r="AG37" s="19">
         <f>Misc!$K$20*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AH37" s="21"/>
       <c r="AI37" s="19">
@@ -8572,7 +8585,7 @@
       </c>
       <c r="AJ37" s="19">
         <f>Misc!$K$21*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AK37" s="21"/>
       <c r="AL37" s="19">
@@ -8581,16 +8594,16 @@
       </c>
       <c r="AM37" s="19">
         <f>Misc!$K$22*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AN37" s="20"/>
       <c r="AO37" s="19">
-        <f>Misc!A35*1.05</f>
-        <v>0</v>
+        <f>Misc!J23*1.05</f>
+        <v>-21</v>
       </c>
       <c r="AP37" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AQ37" s="20"/>
       <c r="AR37" s="19">
@@ -8599,16 +8612,15 @@
       </c>
       <c r="AS37" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AT37" s="20"/>
       <c r="AU37" s="19">
-        <f>Misc!G35*1.05</f>
-        <v>115.5</v>
+        <v>0</v>
       </c>
       <c r="AV37" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AW37" s="20"/>
       <c r="AX37" s="19">
@@ -8617,7 +8629,7 @@
       </c>
       <c r="AY37" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="AZ37" s="20"/>
       <c r="BA37" s="19">
@@ -8626,7 +8638,7 @@
       </c>
       <c r="BB37" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
       <c r="BC37" s="20"/>
       <c r="BD37" s="19">
@@ -8635,7 +8647,7 @@
       </c>
       <c r="BE37" s="19">
         <f>Misc!$K$35*1.05</f>
-        <v>120.75</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="38" spans="1:60" s="1" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -11232,26 +11244,26 @@
         <v>2.6</v>
       </c>
       <c r="AK54" s="21">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AL54" s="19">
         <f>($AK$54*5/Misc!$L$22)-0.1</f>
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AM54" s="19">
         <f>($AK$54*5/Misc!$L$22)+0.1</f>
-        <v>2.6</v>
-      </c>
-      <c r="AN54" s="20">
-        <v>2.56</v>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="AN54" s="21">
+        <v>2.35</v>
       </c>
       <c r="AO54" s="19">
         <f>(AN54*5/Misc!$L$19)-0.1</f>
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AP54" s="19">
         <f>(AN54*5/Misc!$L$19)+0.1</f>
-        <v>2.66</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AQ54" s="20">
         <v>2.56</v>
@@ -11448,16 +11460,16 @@
         <f>($AK$55*5/Misc!$L$22)+0.1</f>
         <v>2.6</v>
       </c>
-      <c r="AN55" s="20">
-        <v>2.7</v>
+      <c r="AN55" s="21">
+        <v>2.5</v>
       </c>
       <c r="AO55" s="19">
         <f>(AN55*5/Misc!$L$19)-0.1</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AP55" s="19">
         <f>(AN55*5/Misc!$L$19)+0.1</f>
-        <v>2.8000000000000003</v>
+        <v>2.6</v>
       </c>
       <c r="AQ55" s="20">
         <v>2.7</v>
@@ -12191,9 +12203,7 @@
         <f>((Misc!$J$28*(222547*Misc!$J$6/(222547+Misc!$J$6)+15750)/((222547*Misc!$J$6/(222547+Misc!$J$6)+15750)+19860))*(5/Misc!$L$21))+0.02</f>
         <v>4.0863153688422091</v>
       </c>
-      <c r="AK60" s="20">
-        <v>4</v>
-      </c>
+      <c r="AK60" s="20"/>
       <c r="AL60" s="19">
         <f>((Misc!$J$28*(219453*Misc!$I$6/(219453+Misc!$I$6)+14250)/((219453*Misc!$I$6/(219453+Misc!$I$6)+14250)+20140))*(5/Misc!$L$22))-0.02</f>
         <v>3.9308479046436471</v>
@@ -12382,9 +12392,7 @@
         <f>((Misc!$K$28*(222547*Misc!$J$6/(222547+Misc!$J$6)+15750)/((222547*Misc!$J$6/(222547+Misc!$J$6)+15750)+19860))*(5/Misc!$L$21))+0.02</f>
         <v>4.1272239741625532</v>
       </c>
-      <c r="AK61" s="20">
-        <v>4</v>
-      </c>
+      <c r="AK61" s="20"/>
       <c r="AL61" s="19">
         <f>((Misc!$K$28*(219453*Misc!$I$6/(219453+Misc!$I$6)+14250)/((219453*Misc!$I$6/(219453+Misc!$I$6)+14250)+20140))*(5/Misc!$L$22))-0.02</f>
         <v>3.9705948654549506</v>
@@ -12642,26 +12650,26 @@
         <v>2.5150000000000001</v>
       </c>
       <c r="AK63" s="20">
-        <v>2.5</v>
+        <v>2.4780000000000002</v>
       </c>
       <c r="AL63" s="19">
         <f>($AK$63*5/Misc!$L$22)-0.015</f>
-        <v>2.4849999999999999</v>
+        <v>2.4630000000000001</v>
       </c>
       <c r="AM63" s="19">
         <f>($AK$63*5/Misc!$L$22)+0.015</f>
-        <v>2.5150000000000001</v>
+        <v>2.4930000000000003</v>
       </c>
       <c r="AN63" s="20">
-        <v>2.4900000000000002</v>
+        <v>2.4780000000000002</v>
       </c>
       <c r="AO63" s="19">
         <f>(AN63*5/Misc!$L$19)-0.015</f>
-        <v>2.4750000000000001</v>
+        <v>2.4630000000000001</v>
       </c>
       <c r="AP63" s="19">
         <f>(AN63*5/Misc!$L$19)+0.015</f>
-        <v>2.5050000000000003</v>
+        <v>2.4930000000000003</v>
       </c>
       <c r="AQ63" s="20">
         <v>2.4900000000000002</v>
@@ -12845,26 +12853,26 @@
         <v>2.5150000000000001</v>
       </c>
       <c r="AK64" s="20">
-        <v>2.5</v>
+        <v>2.484</v>
       </c>
       <c r="AL64" s="19">
         <f>($AK$64*5/Misc!$L$22)-0.015</f>
-        <v>2.4849999999999999</v>
+        <v>2.4689999999999999</v>
       </c>
       <c r="AM64" s="19">
         <f>($AK$64*5/Misc!$L$22)+0.015</f>
-        <v>2.5150000000000001</v>
+        <v>2.4990000000000001</v>
       </c>
       <c r="AN64" s="20">
-        <v>2.4950000000000001</v>
+        <v>2.484</v>
       </c>
       <c r="AO64" s="19">
         <f>(AN64*5/Misc!$L$19)-0.015</f>
-        <v>2.48</v>
+        <v>2.4689999999999999</v>
       </c>
       <c r="AP64" s="19">
         <f>(AN64*5/Misc!$L$19)+0.015</f>
-        <v>2.5100000000000002</v>
+        <v>2.4990000000000001</v>
       </c>
       <c r="AQ64" s="20">
         <v>2.4950000000000001</v>
@@ -15030,15 +15038,15 @@
         <v>11.260863999999996</v>
       </c>
       <c r="AK78" s="21">
-        <v>10.950316666666668</v>
+        <v>10.36</v>
       </c>
       <c r="AL78" s="19">
         <f>(($AK$78)*(5*0.92/Misc!$L$22)-0.02*3.75)-0.65</f>
-        <v>9.349291333333337</v>
+        <v>8.8062000000000022</v>
       </c>
       <c r="AM78" s="19">
         <f>(($AK$78)*(5*1.08/Misc!$L$22)+0.02*3.75)-0.65</f>
-        <v>11.251342000000001</v>
+        <v>10.613799999999999</v>
       </c>
       <c r="AN78" s="20">
         <v>10.56</v>
@@ -15233,15 +15241,15 @@
         <v>11.331352000000001</v>
       </c>
       <c r="AK79" s="21">
-        <v>11.097466666666667</v>
+        <v>10.85</v>
       </c>
       <c r="AL79" s="19">
         <f>(($AK$79)*(5*0.92/Misc!$L$22)-0.02*3.75)-0.65</f>
-        <v>9.4846693333333363</v>
+        <v>9.2570000000000014</v>
       </c>
       <c r="AM79" s="19">
         <f>(($AK$79)*(5*1.08/Misc!$L$22)+0.02*3.75)-0.65</f>
-        <v>11.410264</v>
+        <v>11.142999999999999</v>
       </c>
       <c r="AN79" s="20">
         <v>10.65</v>
@@ -17375,15 +17383,15 @@
         <v>1.53</v>
       </c>
       <c r="AN93" s="20">
-        <v>1.5449999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="AO93" s="19">
         <f>(AN93*5/Misc!$L$19)-0.08</f>
-        <v>1.4649999999999999</v>
+        <v>1.3699999999999999</v>
       </c>
       <c r="AP93" s="19">
         <f>(AN93*5/Misc!$L$19)+0.08</f>
-        <v>1.625</v>
+        <v>1.53</v>
       </c>
       <c r="AQ93" s="20">
         <v>1.5449999999999999</v>
@@ -17581,15 +17589,15 @@
         <v>1.61</v>
       </c>
       <c r="AN94" s="20">
-        <v>1.5629999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="AO94" s="19">
         <f>(AN94*5/Misc!$L$19)-0.08</f>
-        <v>1.4829999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="AP94" s="19">
         <f>(AN94*5/Misc!$L$19)+0.08</f>
-        <v>1.643</v>
+        <v>1.61</v>
       </c>
       <c r="AQ94" s="20">
         <v>1.5629999999999999</v>
@@ -19064,11 +19072,11 @@
       <c r="AK108" s="20">
         <v>1000</v>
       </c>
-      <c r="AL108" s="109">
+      <c r="AL108" s="96">
         <f>$AK$108-8</f>
         <v>992</v>
       </c>
-      <c r="AM108" s="109">
+      <c r="AM108" s="96">
         <f>$AK$108+8</f>
         <v>1008</v>
       </c>
@@ -19267,11 +19275,11 @@
       <c r="AK109" s="20">
         <v>1000</v>
       </c>
-      <c r="AL109" s="109">
+      <c r="AL109" s="96">
         <f>$AK$109-8</f>
         <v>992</v>
       </c>
-      <c r="AM109" s="109">
+      <c r="AM109" s="96">
         <f>$AK$109+8</f>
         <v>1008</v>
       </c>
@@ -19470,11 +19478,11 @@
       <c r="AK110" s="20">
         <v>500</v>
       </c>
-      <c r="AL110" s="109">
+      <c r="AL110" s="96">
         <f>$AK$110-8</f>
         <v>492</v>
       </c>
-      <c r="AM110" s="109">
+      <c r="AM110" s="96">
         <f>$AK$110+8</f>
         <v>508</v>
       </c>
@@ -19673,11 +19681,11 @@
       <c r="AK111" s="20">
         <v>500</v>
       </c>
-      <c r="AL111" s="109">
+      <c r="AL111" s="96">
         <f>$AK$111-8</f>
         <v>492</v>
       </c>
-      <c r="AM111" s="109">
+      <c r="AM111" s="96">
         <f>$AK$111+8</f>
         <v>508</v>
       </c>
@@ -32713,7 +32721,7 @@
       <c r="AN229" s="20"/>
       <c r="AO229" s="19">
         <f>Misc!$M$23</f>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AP229" s="19">
         <f>Misc!$N$23</f>
@@ -33691,16 +33699,16 @@
   <sheetData>
     <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="E4" s="106" t="s">
+      <c r="C4" s="97"/>
+      <c r="E4" s="107" t="s">
         <v>355</v>
       </c>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="109"/>
       <c r="I4" s="84" t="s">
         <v>284</v>
       </c>
@@ -33777,18 +33785,18 @@
       </c>
     </row>
     <row r="9" spans="2:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E9" s="97" t="s">
+      <c r="E9" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="106"/>
     </row>
     <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E10" s="56" t="s">
@@ -33842,7 +33850,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="94">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L11" s="95">
         <v>5</v>
@@ -33874,7 +33882,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="42">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L12" s="47">
         <v>5</v>
@@ -33905,8 +33913,8 @@
       <c r="J13" s="9">
         <v>0</v>
       </c>
-      <c r="K13" s="34">
-        <v>115</v>
+      <c r="K13" s="42">
+        <v>130</v>
       </c>
       <c r="L13" s="47">
         <v>5</v>
@@ -33937,8 +33945,8 @@
       <c r="J14" s="9">
         <v>0</v>
       </c>
-      <c r="K14" s="34">
-        <v>115</v>
+      <c r="K14" s="42">
+        <v>130</v>
       </c>
       <c r="L14" s="47">
         <v>5</v>
@@ -33969,8 +33977,8 @@
       <c r="J15" s="9">
         <v>0</v>
       </c>
-      <c r="K15" s="34">
-        <v>115</v>
+      <c r="K15" s="42">
+        <v>130</v>
       </c>
       <c r="L15" s="47">
         <v>5</v>
@@ -34001,8 +34009,8 @@
       <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="34">
-        <v>115</v>
+      <c r="K16" s="42">
+        <v>130</v>
       </c>
       <c r="L16" s="47">
         <v>5</v>
@@ -34033,8 +34041,8 @@
       <c r="J17" s="9">
         <v>0</v>
       </c>
-      <c r="K17" s="34">
-        <v>115</v>
+      <c r="K17" s="42">
+        <v>130</v>
       </c>
       <c r="L17" s="47">
         <v>5</v>
@@ -34065,8 +34073,8 @@
       <c r="J18" s="9">
         <v>0</v>
       </c>
-      <c r="K18" s="34">
-        <v>115</v>
+      <c r="K18" s="42">
+        <v>130</v>
       </c>
       <c r="L18" s="47">
         <v>5</v>
@@ -34097,8 +34105,8 @@
       <c r="J19" s="9">
         <v>0</v>
       </c>
-      <c r="K19" s="34">
-        <v>115</v>
+      <c r="K19" s="42">
+        <v>130</v>
       </c>
       <c r="L19" s="47">
         <v>5</v>
@@ -34129,8 +34137,8 @@
       <c r="J20" s="9">
         <v>0</v>
       </c>
-      <c r="K20" s="34">
-        <v>115</v>
+      <c r="K20" s="42">
+        <v>130</v>
       </c>
       <c r="L20" s="47">
         <v>5</v>
@@ -34161,8 +34169,8 @@
       <c r="J21" s="9">
         <v>0</v>
       </c>
-      <c r="K21" s="34">
-        <v>115</v>
+      <c r="K21" s="42">
+        <v>130</v>
       </c>
       <c r="L21" s="47">
         <v>5</v>
@@ -34193,8 +34201,8 @@
       <c r="J22" s="9">
         <v>-20</v>
       </c>
-      <c r="K22" s="34">
-        <v>115</v>
+      <c r="K22" s="42">
+        <v>130</v>
       </c>
       <c r="L22" s="47">
         <v>5</v>
@@ -34223,16 +34231,16 @@
         <v>48</v>
       </c>
       <c r="J23" s="64">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="K23" s="36">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L23" s="44">
         <v>5</v>
       </c>
       <c r="M23" s="44">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N23" s="44">
         <v>110</v>
@@ -34240,24 +34248,24 @@
     </row>
     <row r="25" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="5:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E26" s="97" t="s">
+      <c r="E26" s="98" t="s">
         <v>325</v>
       </c>
-      <c r="F26" s="98"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="98"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="98"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="98"/>
-      <c r="N26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="100"/>
     </row>
     <row r="27" spans="5:14" x14ac:dyDescent="0.3">
-      <c r="E27" s="100" t="s">
+      <c r="E27" s="101" t="s">
         <v>326</v>
       </c>
-      <c r="F27" s="101"/>
+      <c r="F27" s="102"/>
       <c r="G27" s="89" t="s">
         <v>318</v>
       </c>
@@ -34284,8 +34292,8 @@
       </c>
     </row>
     <row r="28" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="102"/>
-      <c r="F28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="104"/>
       <c r="G28" s="44">
         <v>2.5</v>
       </c>
@@ -34313,18 +34321,18 @@
     </row>
     <row r="30" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="5:14" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E31" s="97" t="s">
+      <c r="E31" s="98" t="s">
         <v>314</v>
       </c>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="106"/>
     </row>
     <row r="32" spans="5:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E32" s="56" t="s">
@@ -34378,7 +34386,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="32">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L33" s="63">
         <v>5</v>
@@ -34410,7 +34418,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="42">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L34" s="47">
         <v>5</v>
@@ -34442,7 +34450,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="32">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L35" s="63">
         <v>5</v>
@@ -34474,7 +34482,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="42">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L36" s="47">
         <v>5</v>
@@ -34506,7 +34514,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="34">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="L37" s="47">
         <v>5</v>
@@ -34537,15 +34545,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007EAF870E99ECA94F864B327C5B7E3838" ma:contentTypeVersion="31" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="395773d36c2f521a29f182556c34a191">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="04cfd3d3-2c89-4764-aaab-c87677d64949" xmlns:ns3="448318fe-d517-4740-9c4f-0b0645b4226a" xmlns:ns4="50a08be1-ba3e-4a79-8f58-48006bbce96a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fa62a5032f3abd9d41835b1ea6091fec" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="04cfd3d3-2c89-4764-aaab-c87677d64949"/>
@@ -34831,7 +34830,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949">
@@ -34847,15 +34846,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFA3AA9-6430-449F-9930-F36527A7FEB5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6E5232F-F37E-427A-A8C4-17F8B14F4745}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34875,7 +34875,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36E68737-8B0F-4C4C-9FFC-9639EB930D2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="448318fe-d517-4740-9c4f-0b0645b4226a"/>
@@ -34891,4 +34891,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFA3AA9-6430-449F-9930-F36527A7FEB5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/VT LTT Project/Data/Project Database Files/eDCU/48V HighCurrent/Configuration Files/Limit Files/6Head/FE_FF_Frame_Limit_eDCU_Thermal_Endurance_v6.xlsx
+++ b/VT LTT Project/Data/Project Database Files/eDCU/48V HighCurrent/Configuration Files/Limit Files/6Head/FE_FF_Frame_Limit_eDCU_Thermal_Endurance_v6.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eDCU LTT\VT LTT Project\Data\Project Database Files\eDCU\48V HighCurrent\Configuration Files\Limit Files\6Head\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uiv10949\OneDrive - Vitesco Technologies\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E214BF5-CD67-495B-AD62-883B87BBE0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70A209A2-1201-457A-A8EF-392CF68AC305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{49D2488A-EB0E-4C68-8F67-50F12E4C4F72}"/>
   </bookViews>
@@ -2296,15 +2296,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2322,6 +2313,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -2370,7 +2374,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2428,16 +2432,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2566,58 +2564,13 @@
     <xf numFmtId="0" fontId="0" fillId="43" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="42" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="42" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="42" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2636,9 +2589,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2670,6 +2620,51 @@
     </xf>
     <xf numFmtId="1" fontId="21" fillId="44" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="42" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="42" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="42" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3406,164 +3401,164 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="52" t="s">
         <v>337</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="53" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B3" s="56">
+      <c r="B3" s="54">
         <v>1</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="57" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="58" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="56">
+      <c r="B4" s="54">
         <v>2</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="56" t="s">
         <v>343</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="57" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="58" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="61">
+      <c r="B5" s="59">
         <v>3</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="60" t="s">
         <v>345</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="67" t="s">
         <v>347</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="61" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="57">
+      <c r="B6" s="55">
         <v>4</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="62" t="s">
         <v>348</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="68" t="s">
         <v>349</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="61" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="57">
+      <c r="B7" s="55">
         <v>5</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="62" t="s">
         <v>353</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="68" t="s">
         <v>354</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="E7" s="63" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="57">
+      <c r="B8" s="55">
         <v>6</v>
       </c>
-      <c r="C8" s="64" t="s">
+      <c r="C8" s="62" t="s">
         <v>358</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="E8" s="65" t="s">
+      <c r="E8" s="63" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="57">
+      <c r="B9" s="55">
         <v>7</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="62" t="s">
         <v>361</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="E9" s="65" t="s">
+      <c r="E9" s="63" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="57"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="65"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="63"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="57"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="65"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="63"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="57"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="65"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="63"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="57"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="65"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="63"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="57"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="65"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="63"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="57"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="65"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="63"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="57"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="65"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="63"/>
     </row>
     <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="68"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="66"/>
     </row>
   </sheetData>
   <phoneticPr fontId="23" type="noConversion"/>
@@ -3875,12 +3870,12 @@
       </c>
       <c r="AI2" s="14"/>
       <c r="AJ2" s="14"/>
-      <c r="AK2" s="119">
+      <c r="AK2" s="101">
         <v>160</v>
       </c>
       <c r="AL2" s="14"/>
       <c r="AM2" s="14"/>
-      <c r="AN2" s="117">
+      <c r="AN2" s="99">
         <v>160</v>
       </c>
       <c r="AO2" s="14"/>
@@ -3976,12 +3971,12 @@
       </c>
       <c r="AI3" s="14"/>
       <c r="AJ3" s="14"/>
-      <c r="AK3" s="119">
+      <c r="AK3" s="101">
         <v>160</v>
       </c>
       <c r="AL3" s="14"/>
       <c r="AM3" s="14"/>
-      <c r="AN3" s="117">
+      <c r="AN3" s="99">
         <v>160</v>
       </c>
       <c r="AO3" s="14"/>
@@ -4077,12 +4072,12 @@
       </c>
       <c r="AI4" s="14"/>
       <c r="AJ4" s="14"/>
-      <c r="AK4" s="119">
+      <c r="AK4" s="101">
         <v>0</v>
       </c>
       <c r="AL4" s="14"/>
       <c r="AM4" s="14"/>
-      <c r="AN4" s="117">
+      <c r="AN4" s="99">
         <v>0</v>
       </c>
       <c r="AO4" s="14"/>
@@ -4178,12 +4173,12 @@
       </c>
       <c r="AI5" s="14"/>
       <c r="AJ5" s="14"/>
-      <c r="AK5" s="119">
+      <c r="AK5" s="101">
         <v>0</v>
       </c>
       <c r="AL5" s="14"/>
       <c r="AM5" s="14"/>
-      <c r="AN5" s="117">
+      <c r="AN5" s="99">
         <v>0</v>
       </c>
       <c r="AO5" s="14"/>
@@ -4279,12 +4274,12 @@
       </c>
       <c r="AI6" s="14"/>
       <c r="AJ6" s="14"/>
-      <c r="AK6" s="119">
+      <c r="AK6" s="101">
         <v>0</v>
       </c>
       <c r="AL6" s="14"/>
       <c r="AM6" s="14"/>
-      <c r="AN6" s="117">
+      <c r="AN6" s="99">
         <v>0</v>
       </c>
       <c r="AO6" s="14"/>
@@ -4380,12 +4375,12 @@
       </c>
       <c r="AI7" s="14"/>
       <c r="AJ7" s="14"/>
-      <c r="AK7" s="119">
+      <c r="AK7" s="101">
         <v>0</v>
       </c>
       <c r="AL7" s="14"/>
       <c r="AM7" s="14"/>
-      <c r="AN7" s="117">
+      <c r="AN7" s="99">
         <v>0</v>
       </c>
       <c r="AO7" s="14"/>
@@ -4481,12 +4476,12 @@
       </c>
       <c r="AI8" s="14"/>
       <c r="AJ8" s="14"/>
-      <c r="AK8" s="119">
+      <c r="AK8" s="101">
         <v>0</v>
       </c>
       <c r="AL8" s="14"/>
       <c r="AM8" s="14"/>
-      <c r="AN8" s="117">
+      <c r="AN8" s="99">
         <v>0</v>
       </c>
       <c r="AO8" s="14"/>
@@ -4582,12 +4577,12 @@
       </c>
       <c r="AI9" s="14"/>
       <c r="AJ9" s="14"/>
-      <c r="AK9" s="119">
+      <c r="AK9" s="101">
         <v>0</v>
       </c>
       <c r="AL9" s="14"/>
       <c r="AM9" s="14"/>
-      <c r="AN9" s="117">
+      <c r="AN9" s="99">
         <v>0</v>
       </c>
       <c r="AO9" s="14"/>
@@ -4683,12 +4678,12 @@
       </c>
       <c r="AI10" s="14"/>
       <c r="AJ10" s="14"/>
-      <c r="AK10" s="119">
+      <c r="AK10" s="101">
         <v>0</v>
       </c>
       <c r="AL10" s="14"/>
       <c r="AM10" s="14"/>
-      <c r="AN10" s="117">
+      <c r="AN10" s="99">
         <v>0</v>
       </c>
       <c r="AO10" s="14"/>
@@ -4784,12 +4779,12 @@
       </c>
       <c r="AI11" s="14"/>
       <c r="AJ11" s="14"/>
-      <c r="AK11" s="119">
+      <c r="AK11" s="101">
         <v>0</v>
       </c>
       <c r="AL11" s="14"/>
       <c r="AM11" s="14"/>
-      <c r="AN11" s="117">
+      <c r="AN11" s="99">
         <v>0</v>
       </c>
       <c r="AO11" s="14"/>
@@ -4885,12 +4880,12 @@
       </c>
       <c r="AI12" s="14"/>
       <c r="AJ12" s="14"/>
-      <c r="AK12" s="119">
+      <c r="AK12" s="101">
         <v>0</v>
       </c>
       <c r="AL12" s="14"/>
       <c r="AM12" s="14"/>
-      <c r="AN12" s="117">
+      <c r="AN12" s="99">
         <v>0</v>
       </c>
       <c r="AO12" s="14"/>
@@ -4986,12 +4981,12 @@
       </c>
       <c r="AI13" s="14"/>
       <c r="AJ13" s="14"/>
-      <c r="AK13" s="119">
+      <c r="AK13" s="101">
         <v>0</v>
       </c>
       <c r="AL13" s="14"/>
       <c r="AM13" s="14"/>
-      <c r="AN13" s="117">
+      <c r="AN13" s="99">
         <v>0</v>
       </c>
       <c r="AO13" s="14"/>
@@ -5087,12 +5082,12 @@
       </c>
       <c r="AI14" s="14"/>
       <c r="AJ14" s="14"/>
-      <c r="AK14" s="119">
+      <c r="AK14" s="101">
         <v>160</v>
       </c>
       <c r="AL14" s="14"/>
       <c r="AM14" s="14"/>
-      <c r="AN14" s="117">
+      <c r="AN14" s="99">
         <v>160</v>
       </c>
       <c r="AO14" s="14"/>
@@ -5124,7 +5119,7 @@
       <c r="BE14" s="14"/>
     </row>
     <row r="15" spans="1:58" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39">
+      <c r="A15" s="37">
         <v>14</v>
       </c>
       <c r="B15" s="21" t="s">
@@ -5248,18 +5243,18 @@
         <f>($AH$15*5/Misc!$L$21)+0.1</f>
         <v>2.66</v>
       </c>
-      <c r="AK15" s="117">
+      <c r="AK15" s="99">
         <v>2.3610000000000002</v>
       </c>
       <c r="AL15" s="14">
-        <f>($AK$15*5/Misc!$L$22)-0.1</f>
-        <v>2.2610000000000001</v>
+        <f>($AK$15*5/Misc!$L$22)-0.15</f>
+        <v>2.2110000000000003</v>
       </c>
       <c r="AM15" s="14">
-        <f>($AK$15*5/Misc!$L$22)+0.1</f>
-        <v>2.4610000000000003</v>
-      </c>
-      <c r="AN15" s="117">
+        <f>($AK$15*5/Misc!$L$22)+0.15</f>
+        <v>2.5110000000000001</v>
+      </c>
+      <c r="AN15" s="99">
         <v>2.379</v>
       </c>
       <c r="AO15" s="14">
@@ -5327,7 +5322,7 @@
       </c>
     </row>
     <row r="16" spans="1:58" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39">
+      <c r="A16" s="37">
         <v>15</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -5451,18 +5446,18 @@
         <f>($AH$16*5/Misc!$L$21)+0.1</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="AK16" s="117">
+      <c r="AK16" s="99">
         <v>2.5510000000000002</v>
       </c>
       <c r="AL16" s="14">
-        <f>($AK$16*5/Misc!$L$22)-0.1</f>
-        <v>2.4510000000000001</v>
+        <f>($AK$16*5/Misc!$L$22)-0.15</f>
+        <v>2.4010000000000002</v>
       </c>
       <c r="AM16" s="14">
-        <f>($AK$16*5/Misc!$L$22)+0.1</f>
-        <v>2.6510000000000002</v>
-      </c>
-      <c r="AN16" s="117">
+        <f>($AK$16*5/Misc!$L$22)+0.15</f>
+        <v>2.7010000000000001</v>
+      </c>
+      <c r="AN16" s="99">
         <v>2.5</v>
       </c>
       <c r="AO16" s="14">
@@ -5572,10 +5567,10 @@
       <c r="AH17" s="16"/>
       <c r="AI17" s="14"/>
       <c r="AJ17" s="14"/>
-      <c r="AK17" s="118"/>
+      <c r="AK17" s="100"/>
       <c r="AL17" s="14"/>
       <c r="AM17" s="14"/>
-      <c r="AN17" s="117"/>
+      <c r="AN17" s="99"/>
       <c r="AO17" s="14"/>
       <c r="AP17" s="14"/>
       <c r="AQ17" s="15"/>
@@ -5719,7 +5714,7 @@
         <f>($AH$18*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK18" s="118">
+      <c r="AK18" s="100">
         <v>2.5</v>
       </c>
       <c r="AL18" s="14">
@@ -5730,7 +5725,7 @@
         <f>($AK$18*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN18" s="117">
+      <c r="AN18" s="99">
         <v>2.5</v>
       </c>
       <c r="AO18" s="14">
@@ -5922,7 +5917,7 @@
         <f>($AH$19*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK19" s="118">
+      <c r="AK19" s="100">
         <v>2.5</v>
       </c>
       <c r="AL19" s="14">
@@ -5933,7 +5928,7 @@
         <f>($AK$19*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN19" s="117">
+      <c r="AN19" s="99">
         <v>2.5</v>
       </c>
       <c r="AO19" s="14">
@@ -6043,10 +6038,10 @@
       <c r="AH20" s="16"/>
       <c r="AI20" s="14"/>
       <c r="AJ20" s="14"/>
-      <c r="AK20" s="118"/>
+      <c r="AK20" s="100"/>
       <c r="AL20" s="14"/>
       <c r="AM20" s="14"/>
-      <c r="AN20" s="117"/>
+      <c r="AN20" s="99"/>
       <c r="AO20" s="14"/>
       <c r="AP20" s="14"/>
       <c r="AQ20" s="15"/>
@@ -6182,26 +6177,26 @@
       <c r="AH21" s="15">
         <v>0.72</v>
       </c>
-      <c r="AI21" s="43">
+      <c r="AI21" s="41">
         <f>(Misc!$J$28*14250/(14250+20140+(Misc!$J$6*222547/(Misc!$J$6+222547))))*(5/Misc!$L$21)-0.02</f>
         <v>0.635738595489858</v>
       </c>
-      <c r="AJ21" s="43">
+      <c r="AJ21" s="41">
         <f>(Misc!$J$28*15750/(15750+19860+(Misc!$I$6*219453/(Misc!$I$6+219453))))*(5/Misc!$L$21)+0.02</f>
         <v>0.80722454153136702</v>
       </c>
-      <c r="AK21" s="117">
+      <c r="AK21" s="99">
         <v>0.72</v>
       </c>
-      <c r="AL21" s="43">
+      <c r="AL21" s="41">
         <f>(Misc!$J$28*14250/(14250+20140+(Misc!$J$6*222547/(Misc!$J$6+222547))))*(5/Misc!$L$22)-0.02</f>
         <v>0.635738595489858</v>
       </c>
-      <c r="AM21" s="43">
+      <c r="AM21" s="41">
         <f>(Misc!$J$28*15750/(15750+19860+(Misc!$I$6*219453/(Misc!$I$6+219453))))*(5/Misc!$L$22)+0.02</f>
         <v>0.80722454153136702</v>
       </c>
-      <c r="AN21" s="117">
+      <c r="AN21" s="99">
         <v>0.72</v>
       </c>
       <c r="AO21" s="14">
@@ -6385,26 +6380,26 @@
       <c r="AH22" s="15">
         <v>0.72</v>
       </c>
-      <c r="AI22" s="43">
+      <c r="AI22" s="41">
         <f>(Misc!$K$28*14250/(14250+20140+(Misc!$J$6*222547/(Misc!$J$6+222547))))*(5/Misc!$L$21)-0.02</f>
         <v>0.64233556325132546</v>
       </c>
-      <c r="AJ22" s="43">
+      <c r="AJ22" s="41">
         <f>(Misc!$K$28*15750/(15750+19860+(Misc!$I$6*219453/(Misc!$I$6+219453))))*(5/Misc!$L$21)+0.02</f>
         <v>0.81514430553067652</v>
       </c>
-      <c r="AK22" s="117">
+      <c r="AK22" s="99">
         <v>0.72</v>
       </c>
-      <c r="AL22" s="43">
+      <c r="AL22" s="41">
         <f>(Misc!$K$28*14250/(14250+20140+(Misc!$J$6*222547/(Misc!$J$6+222547))))*(5/Misc!$L$22)-0.02</f>
         <v>0.64233556325132546</v>
       </c>
-      <c r="AM22" s="43">
+      <c r="AM22" s="41">
         <f>(Misc!$K$28*15750/(15750+19860+(Misc!$I$6*219453/(Misc!$I$6+219453))))*(5/Misc!$L$22)+0.02</f>
         <v>0.81514430553067652</v>
       </c>
-      <c r="AN22" s="117">
+      <c r="AN22" s="99">
         <v>0.72</v>
       </c>
       <c r="AO22" s="14">
@@ -6514,10 +6509,10 @@
       <c r="AH23" s="16"/>
       <c r="AI23" s="14"/>
       <c r="AJ23" s="14"/>
-      <c r="AK23" s="118"/>
+      <c r="AK23" s="100"/>
       <c r="AL23" s="14"/>
       <c r="AM23" s="14"/>
-      <c r="AN23" s="117"/>
+      <c r="AN23" s="99"/>
       <c r="AO23" s="14"/>
       <c r="AP23" s="14"/>
       <c r="AQ23" s="15"/>
@@ -6537,7 +6532,7 @@
       <c r="BE23" s="14"/>
     </row>
     <row r="24" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39">
+      <c r="A24" s="37">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -6661,18 +6656,18 @@
         <f>($AH$24*5/Misc!$L$21)+0.015</f>
         <v>2.5020000000000002</v>
       </c>
-      <c r="AK24" s="117">
+      <c r="AK24" s="99">
         <v>2.4860000000000002</v>
       </c>
       <c r="AL24" s="14">
-        <f>($AK$24*5/Misc!$L$22)-0.015</f>
-        <v>2.4710000000000001</v>
+        <f>($AK$24*5/Misc!$L$22)-0.015-0.1</f>
+        <v>2.371</v>
       </c>
       <c r="AM24" s="14">
-        <f>($AK$24*5/Misc!$L$22)+0.015</f>
-        <v>2.5010000000000003</v>
-      </c>
-      <c r="AN24" s="117">
+        <f>($AK$24*5/Misc!$L$22)+0.015+0.1</f>
+        <v>2.6010000000000004</v>
+      </c>
+      <c r="AN24" s="99">
         <v>2.4860000000000002</v>
       </c>
       <c r="AO24" s="14">
@@ -6740,7 +6735,7 @@
       </c>
     </row>
     <row r="25" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39">
+      <c r="A25" s="37">
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -6864,18 +6859,18 @@
         <f>($AH$25*5/Misc!$L$21)+0.015</f>
         <v>2.5050000000000003</v>
       </c>
-      <c r="AK25" s="117">
+      <c r="AK25" s="99">
         <v>2.4910000000000001</v>
       </c>
       <c r="AL25" s="14">
-        <f>($AK$25*5/Misc!$L$22)-0.015</f>
-        <v>2.476</v>
+        <f>($AK$25*5/Misc!$L$22)-0.015-0.1</f>
+        <v>2.3759999999999999</v>
       </c>
       <c r="AM25" s="14">
-        <f>($AK$25*5/Misc!$L$22)+0.015</f>
-        <v>2.5060000000000002</v>
-      </c>
-      <c r="AN25" s="117">
+        <f>($AK$25*5/Misc!$L$22)+0.015+0.1</f>
+        <v>2.6060000000000003</v>
+      </c>
+      <c r="AN25" s="99">
         <v>2.4910000000000001</v>
       </c>
       <c r="AO25" s="14">
@@ -6985,10 +6980,10 @@
       <c r="AH26" s="16"/>
       <c r="AI26" s="14"/>
       <c r="AJ26" s="14"/>
-      <c r="AK26" s="118"/>
+      <c r="AK26" s="100"/>
       <c r="AL26" s="14"/>
       <c r="AM26" s="14"/>
-      <c r="AN26" s="117"/>
+      <c r="AN26" s="99"/>
       <c r="AO26" s="14"/>
       <c r="AP26" s="14"/>
       <c r="AQ26" s="15"/>
@@ -7132,7 +7127,7 @@
         <f>(Misc!$H$28)*(5*1.008/Misc!$L$21)+0.02*1.1</f>
         <v>5.0317600000000002</v>
       </c>
-      <c r="AK27" s="118">
+      <c r="AK27" s="100">
         <v>4.9950000000000001</v>
       </c>
       <c r="AL27" s="14">
@@ -7143,7 +7138,7 @@
         <f>(Misc!$H$28)*(5*1.008/Misc!$L$22)+0.02*1.1</f>
         <v>5.0317600000000002</v>
       </c>
-      <c r="AN27" s="117"/>
+      <c r="AN27" s="99"/>
       <c r="AO27" s="14">
         <f>(Misc!$H$28)*(5*0.99/Misc!$L$19)-0.02*1.1</f>
         <v>4.8982999999999999</v>
@@ -7323,7 +7318,7 @@
         <f>(Misc!$I$28)*(5*1.008/Misc!$L$21)+0.02*1.1</f>
         <v>5.08216</v>
       </c>
-      <c r="AK28" s="118">
+      <c r="AK28" s="100">
         <v>5</v>
       </c>
       <c r="AL28" s="14">
@@ -7334,7 +7329,7 @@
         <f>(Misc!$I$28)*(5*1.008/Misc!$L$22)+0.02*1.1</f>
         <v>5.08216</v>
       </c>
-      <c r="AN28" s="117"/>
+      <c r="AN28" s="99"/>
       <c r="AO28" s="14">
         <f>(Misc!$I$28)*(5*0.99/Misc!$L$19)-0.02*1.1</f>
         <v>4.9477999999999991</v>
@@ -7432,10 +7427,10 @@
       <c r="AH29" s="16"/>
       <c r="AI29" s="14"/>
       <c r="AJ29" s="14"/>
-      <c r="AK29" s="118"/>
+      <c r="AK29" s="100"/>
       <c r="AL29" s="14"/>
       <c r="AM29" s="14"/>
-      <c r="AN29" s="117"/>
+      <c r="AN29" s="99"/>
       <c r="AO29" s="14"/>
       <c r="AP29" s="14"/>
       <c r="AQ29" s="15"/>
@@ -7579,7 +7574,7 @@
         <f>($AH$30*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK30" s="118">
+      <c r="AK30" s="100">
         <v>2.5</v>
       </c>
       <c r="AL30" s="14">
@@ -7590,7 +7585,7 @@
         <f>($AK$30*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN30" s="117">
+      <c r="AN30" s="99">
         <v>2.5</v>
       </c>
       <c r="AO30" s="14">
@@ -7782,7 +7777,7 @@
         <f>($AH$31*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK31" s="118">
+      <c r="AK31" s="100">
         <v>2.5</v>
       </c>
       <c r="AL31" s="14">
@@ -7793,7 +7788,7 @@
         <f>($AK$31*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN31" s="117">
+      <c r="AN31" s="99">
         <v>2.5</v>
       </c>
       <c r="AO31" s="14">
@@ -7903,10 +7898,10 @@
       <c r="AH32" s="16"/>
       <c r="AI32" s="14"/>
       <c r="AJ32" s="14"/>
-      <c r="AK32" s="118"/>
+      <c r="AK32" s="100"/>
       <c r="AL32" s="14"/>
       <c r="AM32" s="14"/>
-      <c r="AN32" s="117"/>
+      <c r="AN32" s="99"/>
       <c r="AO32" s="14"/>
       <c r="AP32" s="14"/>
       <c r="AQ32" s="15"/>
@@ -8050,7 +8045,7 @@
         <f>($AH$33*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK33" s="118">
+      <c r="AK33" s="100">
         <v>2.5</v>
       </c>
       <c r="AL33" s="14">
@@ -8061,7 +8056,7 @@
         <f>($AK$33*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN33" s="117">
+      <c r="AN33" s="99">
         <v>2.5</v>
       </c>
       <c r="AO33" s="14">
@@ -8253,7 +8248,7 @@
         <f>($AH$34*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK34" s="118">
+      <c r="AK34" s="100">
         <v>2.5</v>
       </c>
       <c r="AL34" s="14">
@@ -8264,7 +8259,7 @@
         <f>($AK$34*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN34" s="117">
+      <c r="AN34" s="99">
         <v>2.5</v>
       </c>
       <c r="AO34" s="14">
@@ -8374,10 +8369,10 @@
       <c r="AH35" s="16"/>
       <c r="AI35" s="14"/>
       <c r="AJ35" s="14"/>
-      <c r="AK35" s="118"/>
+      <c r="AK35" s="100"/>
       <c r="AL35" s="14"/>
       <c r="AM35" s="14"/>
-      <c r="AN35" s="117"/>
+      <c r="AN35" s="99"/>
       <c r="AO35" s="14"/>
       <c r="AP35" s="14"/>
       <c r="AQ35" s="15"/>
@@ -8397,7 +8392,7 @@
       <c r="BE35" s="14"/>
     </row>
     <row r="36" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="39">
+      <c r="A36" s="37">
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
@@ -8418,7 +8413,7 @@
       </c>
       <c r="I36" s="14">
         <f>Misc!$K$12*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="J36" s="15"/>
       <c r="K36" s="14">
@@ -8427,7 +8422,7 @@
       </c>
       <c r="L36" s="14">
         <f>Misc!$K$13*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="14">
@@ -8436,7 +8431,7 @@
       </c>
       <c r="O36" s="14">
         <f>Misc!$K$14*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="P36" s="15"/>
       <c r="Q36" s="14">
@@ -8445,7 +8440,7 @@
       </c>
       <c r="R36" s="14">
         <f>Misc!$K$15*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="S36" s="15"/>
       <c r="T36" s="14">
@@ -8454,7 +8449,7 @@
       </c>
       <c r="U36" s="14">
         <f>Misc!$K$16*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="V36" s="15"/>
       <c r="W36" s="14">
@@ -8463,7 +8458,7 @@
       </c>
       <c r="X36" s="14">
         <f>Misc!$K$17*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="Y36" s="15"/>
       <c r="Z36" s="14">
@@ -8472,7 +8467,7 @@
       </c>
       <c r="AA36" s="14">
         <f>Misc!$K$18*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AB36" s="15"/>
       <c r="AC36" s="14">
@@ -8481,7 +8476,7 @@
       </c>
       <c r="AD36" s="14">
         <f>Misc!$K$19*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AE36" s="15"/>
       <c r="AF36" s="14">
@@ -8490,7 +8485,7 @@
       </c>
       <c r="AG36" s="14">
         <f>Misc!$K$20*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AH36" s="16"/>
       <c r="AI36" s="14">
@@ -8499,25 +8494,25 @@
       </c>
       <c r="AJ36" s="14">
         <f>Misc!$K$21*1.05</f>
-        <v>126</v>
-      </c>
-      <c r="AK36" s="118"/>
+        <v>124.95</v>
+      </c>
+      <c r="AK36" s="100"/>
       <c r="AL36" s="14">
-        <f>Misc!$J$22*1.05</f>
-        <v>-21</v>
+        <f>Misc!$J$22*1.1</f>
+        <v>-22</v>
       </c>
       <c r="AM36" s="14">
         <f>Misc!$K$22*1.05</f>
-        <v>126</v>
-      </c>
-      <c r="AN36" s="117"/>
+        <v>124.95</v>
+      </c>
+      <c r="AN36" s="99"/>
       <c r="AO36" s="14">
         <f>Misc!J23*1.05</f>
         <v>-21</v>
       </c>
       <c r="AP36" s="14">
         <f>Misc!$K$23*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AQ36" s="15"/>
       <c r="AR36" s="14">
@@ -8565,7 +8560,7 @@
       </c>
     </row>
     <row r="37" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="39">
+      <c r="A37" s="37">
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
@@ -8586,7 +8581,7 @@
       </c>
       <c r="I37" s="14">
         <f>Misc!$K$12*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="J37" s="15"/>
       <c r="K37" s="14">
@@ -8595,7 +8590,7 @@
       </c>
       <c r="L37" s="14">
         <f>Misc!$K$13*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="M37" s="15"/>
       <c r="N37" s="14">
@@ -8604,7 +8599,7 @@
       </c>
       <c r="O37" s="14">
         <f>Misc!$K$14*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="14">
@@ -8613,7 +8608,7 @@
       </c>
       <c r="R37" s="14">
         <f>Misc!$K$15*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="S37" s="15"/>
       <c r="T37" s="14">
@@ -8622,7 +8617,7 @@
       </c>
       <c r="U37" s="14">
         <f>Misc!$K$16*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="V37" s="15"/>
       <c r="W37" s="14">
@@ -8631,7 +8626,7 @@
       </c>
       <c r="X37" s="14">
         <f>Misc!$K$17*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="Y37" s="15"/>
       <c r="Z37" s="14">
@@ -8640,7 +8635,7 @@
       </c>
       <c r="AA37" s="14">
         <f>Misc!$K$18*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AB37" s="15"/>
       <c r="AC37" s="14">
@@ -8649,7 +8644,7 @@
       </c>
       <c r="AD37" s="14">
         <f>Misc!$K$19*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AE37" s="15"/>
       <c r="AF37" s="14">
@@ -8658,7 +8653,7 @@
       </c>
       <c r="AG37" s="14">
         <f>Misc!$K$20*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AH37" s="16"/>
       <c r="AI37" s="14">
@@ -8667,25 +8662,25 @@
       </c>
       <c r="AJ37" s="14">
         <f>Misc!$K$21*1.05</f>
-        <v>126</v>
-      </c>
-      <c r="AK37" s="118"/>
+        <v>124.95</v>
+      </c>
+      <c r="AK37" s="100"/>
       <c r="AL37" s="14">
-        <f>Misc!$J$22*1.05</f>
-        <v>-21</v>
+        <f>Misc!$J$22*1.1</f>
+        <v>-22</v>
       </c>
       <c r="AM37" s="14">
         <f>Misc!$K$22*1.05</f>
-        <v>126</v>
-      </c>
-      <c r="AN37" s="117"/>
+        <v>124.95</v>
+      </c>
+      <c r="AN37" s="99"/>
       <c r="AO37" s="14">
         <f>Misc!J23*1.05</f>
         <v>-21</v>
       </c>
       <c r="AP37" s="14">
         <f>Misc!$K$23*1.05</f>
-        <v>126</v>
+        <v>124.95</v>
       </c>
       <c r="AQ37" s="15"/>
       <c r="AR37" s="14">
@@ -8775,10 +8770,10 @@
       <c r="AH38" s="16"/>
       <c r="AI38" s="14"/>
       <c r="AJ38" s="14"/>
-      <c r="AK38" s="118"/>
+      <c r="AK38" s="100"/>
       <c r="AL38" s="14"/>
       <c r="AM38" s="14"/>
-      <c r="AN38" s="117"/>
+      <c r="AN38" s="99"/>
       <c r="AO38" s="14"/>
       <c r="AP38" s="14"/>
       <c r="AQ38" s="15"/>
@@ -8922,18 +8917,18 @@
         <f>($AH$39*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK39" s="118">
+      <c r="AK39" s="100">
         <v>2.5</v>
       </c>
       <c r="AL39" s="14">
-        <f>($AK$39*5*0.93058/Misc!$L$22)-0.02*3.4</f>
-        <v>2.2584499999999998</v>
+        <f>($AK$39*5*0.93058/Misc!$L$22)-0.02*3.4-0.1</f>
+        <v>2.1584499999999998</v>
       </c>
       <c r="AM39" s="14">
         <f>($AK$39*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN39" s="117">
+      <c r="AN39" s="99">
         <v>2.5</v>
       </c>
       <c r="AO39" s="14">
@@ -9125,18 +9120,18 @@
         <f>($AH$40*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK40" s="118">
+      <c r="AK40" s="100">
         <v>2.5</v>
       </c>
       <c r="AL40" s="14">
-        <f>($AK$40*5*0.93058/Misc!$L$22)-0.02*3.4</f>
-        <v>2.2584499999999998</v>
+        <f>($AK$40*5*0.93058/Misc!$L$22)-0.02*3.4-0.1</f>
+        <v>2.1584499999999998</v>
       </c>
       <c r="AM40" s="14">
         <f>($AK$40*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN40" s="117">
+      <c r="AN40" s="99">
         <v>2.5</v>
       </c>
       <c r="AO40" s="14">
@@ -9246,10 +9241,10 @@
       <c r="AH41" s="16"/>
       <c r="AI41" s="14"/>
       <c r="AJ41" s="14"/>
-      <c r="AK41" s="118"/>
+      <c r="AK41" s="100"/>
       <c r="AL41" s="14"/>
       <c r="AM41" s="14"/>
-      <c r="AN41" s="117"/>
+      <c r="AN41" s="99"/>
       <c r="AO41" s="14"/>
       <c r="AP41" s="14"/>
       <c r="AQ41" s="15"/>
@@ -9393,7 +9388,7 @@
         <f>($AH$42*5*1.064/Misc!$L$21)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AK42" s="118">
+      <c r="AK42" s="100">
         <v>2.5</v>
       </c>
       <c r="AL42" s="14">
@@ -9404,7 +9399,7 @@
         <f>($AK$42*5*1.064/Misc!$L$22)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AN42" s="117">
+      <c r="AN42" s="99">
         <v>2.5</v>
       </c>
       <c r="AO42" s="14">
@@ -9596,7 +9591,7 @@
         <f>($AH$43*5*1.064/Misc!$L$21)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AK43" s="118">
+      <c r="AK43" s="100">
         <v>2.5</v>
       </c>
       <c r="AL43" s="14">
@@ -9607,7 +9602,7 @@
         <f>($AK$43*5*1.064/Misc!$L$22)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AN43" s="117">
+      <c r="AN43" s="99">
         <v>2.5</v>
       </c>
       <c r="AO43" s="14">
@@ -9717,10 +9712,10 @@
       <c r="AH44" s="16"/>
       <c r="AI44" s="14"/>
       <c r="AJ44" s="14"/>
-      <c r="AK44" s="118"/>
+      <c r="AK44" s="100"/>
       <c r="AL44" s="14"/>
       <c r="AM44" s="14"/>
-      <c r="AN44" s="117"/>
+      <c r="AN44" s="99"/>
       <c r="AO44" s="14"/>
       <c r="AP44" s="14"/>
       <c r="AQ44" s="15"/>
@@ -9864,7 +9859,7 @@
         <f>($AH$45*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK45" s="118">
+      <c r="AK45" s="100">
         <v>2.5</v>
       </c>
       <c r="AL45" s="14">
@@ -9875,7 +9870,7 @@
         <f>($AK$45*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN45" s="117">
+      <c r="AN45" s="99">
         <v>2.5</v>
       </c>
       <c r="AO45" s="14">
@@ -10067,7 +10062,7 @@
         <f>($AH$46*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK46" s="118">
+      <c r="AK46" s="100">
         <v>2.5</v>
       </c>
       <c r="AL46" s="14">
@@ -10078,7 +10073,7 @@
         <f>($AK$46*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN46" s="117">
+      <c r="AN46" s="99">
         <v>2.5</v>
       </c>
       <c r="AO46" s="14">
@@ -10188,10 +10183,10 @@
       <c r="AH47" s="16"/>
       <c r="AI47" s="14"/>
       <c r="AJ47" s="14"/>
-      <c r="AK47" s="118"/>
+      <c r="AK47" s="100"/>
       <c r="AL47" s="14"/>
       <c r="AM47" s="14"/>
-      <c r="AN47" s="117"/>
+      <c r="AN47" s="99"/>
       <c r="AO47" s="14"/>
       <c r="AP47" s="14"/>
       <c r="AQ47" s="15"/>
@@ -10335,7 +10330,7 @@
         <f>($AH$48*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK48" s="118">
+      <c r="AK48" s="100">
         <v>2.5</v>
       </c>
       <c r="AL48" s="14">
@@ -10346,7 +10341,7 @@
         <f>($AK$48*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN48" s="117">
+      <c r="AN48" s="99">
         <v>2.5</v>
       </c>
       <c r="AO48" s="14">
@@ -10538,7 +10533,7 @@
         <f>($AH$49*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK49" s="118">
+      <c r="AK49" s="100">
         <v>2.5</v>
       </c>
       <c r="AL49" s="14">
@@ -10549,7 +10544,7 @@
         <f>($AK$49*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN49" s="117">
+      <c r="AN49" s="99">
         <v>2.5</v>
       </c>
       <c r="AO49" s="14">
@@ -10659,10 +10654,10 @@
       <c r="AH50" s="16"/>
       <c r="AI50" s="14"/>
       <c r="AJ50" s="14"/>
-      <c r="AK50" s="118"/>
+      <c r="AK50" s="100"/>
       <c r="AL50" s="14"/>
       <c r="AM50" s="14"/>
-      <c r="AN50" s="117"/>
+      <c r="AN50" s="99"/>
       <c r="AO50" s="14"/>
       <c r="AP50" s="14"/>
       <c r="AQ50" s="15"/>
@@ -10806,7 +10801,7 @@
         <f>($AH$51*5*1.064/Misc!$L$21)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AK51" s="118">
+      <c r="AK51" s="100">
         <v>2.5</v>
       </c>
       <c r="AL51" s="14">
@@ -10817,7 +10812,7 @@
         <f>($AK$51*5*1.064/Misc!$L$22)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AN51" s="117">
+      <c r="AN51" s="99">
         <v>2.5</v>
       </c>
       <c r="AO51" s="14">
@@ -11009,7 +11004,7 @@
         <f>($AH$52*5*1.064/Misc!$L$21)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AK52" s="118">
+      <c r="AK52" s="100">
         <v>2.5</v>
       </c>
       <c r="AL52" s="14">
@@ -11020,7 +11015,7 @@
         <f>($AK$52*5*1.064/Misc!$L$22)+0.02*2.8</f>
         <v>2.7160000000000002</v>
       </c>
-      <c r="AN52" s="117">
+      <c r="AN52" s="99">
         <v>2.5</v>
       </c>
       <c r="AO52" s="14">
@@ -11130,10 +11125,10 @@
       <c r="AH53" s="16"/>
       <c r="AI53" s="14"/>
       <c r="AJ53" s="14"/>
-      <c r="AK53" s="118"/>
+      <c r="AK53" s="100"/>
       <c r="AL53" s="14"/>
       <c r="AM53" s="14"/>
-      <c r="AN53" s="117"/>
+      <c r="AN53" s="99"/>
       <c r="AO53" s="14"/>
       <c r="AP53" s="14"/>
       <c r="AQ53" s="15"/>
@@ -11153,7 +11148,7 @@
       <c r="BE53" s="14"/>
     </row>
     <row r="54" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="39">
+      <c r="A54" s="37">
         <v>53</v>
       </c>
       <c r="B54" s="21" t="s">
@@ -11277,27 +11272,27 @@
         <f>($AH$54*5/Misc!$L$21)+0.1</f>
         <v>2.6</v>
       </c>
-      <c r="AK54" s="118">
+      <c r="AK54" s="100">
         <v>2.3570000000000002</v>
       </c>
       <c r="AL54" s="14">
-        <f>($AK$54*5/Misc!$L$22)-0.1</f>
-        <v>2.2570000000000001</v>
+        <f>($AK$54*5/Misc!$L$22)-0.15</f>
+        <v>2.2070000000000003</v>
       </c>
       <c r="AM54" s="14">
-        <f>($AK$54*5/Misc!$L$22)+0.1</f>
-        <v>2.4570000000000003</v>
-      </c>
-      <c r="AN54" s="118">
+        <f>($AK$54*5/Misc!$L$22)+0.15</f>
+        <v>2.5070000000000001</v>
+      </c>
+      <c r="AN54" s="100">
         <v>2.35</v>
       </c>
       <c r="AO54" s="14">
-        <f>(AN54*5/Misc!$L$19)-0.1</f>
-        <v>2.25</v>
+        <f>(AN54*5/Misc!$L$19)-0.15</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AP54" s="14">
-        <f>(AN54*5/Misc!$L$19)+0.1</f>
-        <v>2.4500000000000002</v>
+        <f>(AN54*5/Misc!$L$19)+0.15</f>
+        <v>2.5</v>
       </c>
       <c r="AQ54" s="15">
         <v>2.56</v>
@@ -11356,7 +11351,7 @@
       </c>
     </row>
     <row r="55" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="39">
+      <c r="A55" s="37">
         <v>54</v>
       </c>
       <c r="B55" s="21" t="s">
@@ -11480,27 +11475,27 @@
         <f>($AH$55*5/Misc!$L$21)+0.1</f>
         <v>2.6</v>
       </c>
-      <c r="AK55" s="118">
+      <c r="AK55" s="100">
         <v>2.556</v>
       </c>
       <c r="AL55" s="14">
-        <f>($AK$55*5/Misc!$L$22)-0.1</f>
-        <v>2.456</v>
+        <f>($AK$55*5/Misc!$L$22)-0.15</f>
+        <v>2.4060000000000001</v>
       </c>
       <c r="AM55" s="14">
-        <f>($AK$55*5/Misc!$L$22)+0.1</f>
-        <v>2.6560000000000001</v>
-      </c>
-      <c r="AN55" s="118">
+        <f>($AK$55*5/Misc!$L$22)+0.15</f>
+        <v>2.706</v>
+      </c>
+      <c r="AN55" s="100">
         <v>2.5499999999999998</v>
       </c>
       <c r="AO55" s="14">
-        <f>(AN55*5/Misc!$L$19)-0.1</f>
-        <v>2.4499999999999997</v>
+        <f>(AN55*5/Misc!$L$19)-0.15</f>
+        <v>2.4</v>
       </c>
       <c r="AP55" s="14">
-        <f>(AN55*5/Misc!$L$19)+0.1</f>
-        <v>2.65</v>
+        <f>(AN55*5/Misc!$L$19)+0.15</f>
+        <v>2.6999999999999997</v>
       </c>
       <c r="AQ55" s="15">
         <v>2.7</v>
@@ -11601,10 +11596,10 @@
       <c r="AH56" s="16"/>
       <c r="AI56" s="14"/>
       <c r="AJ56" s="14"/>
-      <c r="AK56" s="118"/>
+      <c r="AK56" s="100"/>
       <c r="AL56" s="14"/>
       <c r="AM56" s="14"/>
-      <c r="AN56" s="117"/>
+      <c r="AN56" s="99"/>
       <c r="AO56" s="14"/>
       <c r="AP56" s="14"/>
       <c r="AQ56" s="15"/>
@@ -11748,7 +11743,7 @@
         <f>($AH$57*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK57" s="118">
+      <c r="AK57" s="100">
         <v>2.5</v>
       </c>
       <c r="AL57" s="14">
@@ -11759,7 +11754,7 @@
         <f>($AK$57*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN57" s="117">
+      <c r="AN57" s="99">
         <v>2.5</v>
       </c>
       <c r="AO57" s="14">
@@ -11951,7 +11946,7 @@
         <f>($AH$58*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK58" s="118">
+      <c r="AK58" s="100">
         <v>2.5</v>
       </c>
       <c r="AL58" s="14">
@@ -11962,7 +11957,7 @@
         <f>($AK$58*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN58" s="117">
+      <c r="AN58" s="99">
         <v>2.5</v>
       </c>
       <c r="AO58" s="14">
@@ -12072,10 +12067,10 @@
       <c r="AH59" s="16"/>
       <c r="AI59" s="14"/>
       <c r="AJ59" s="14"/>
-      <c r="AK59" s="118"/>
+      <c r="AK59" s="100"/>
       <c r="AL59" s="14"/>
       <c r="AM59" s="14"/>
-      <c r="AN59" s="117"/>
+      <c r="AN59" s="99"/>
       <c r="AO59" s="14"/>
       <c r="AP59" s="14"/>
       <c r="AQ59" s="15"/>
@@ -12219,7 +12214,7 @@
         <f>((Misc!$J$28*(222547*Misc!$J$6/(222547+Misc!$J$6)+15750)/((222547*Misc!$J$6/(222547+Misc!$J$6)+15750)+19860))*(5/Misc!$L$21))+0.02</f>
         <v>4.0863153688422091</v>
       </c>
-      <c r="AK60" s="117"/>
+      <c r="AK60" s="99"/>
       <c r="AL60" s="14">
         <f>((Misc!$J$28*(219453*Misc!$I$6/(219453+Misc!$I$6)+14250)/((219453*Misc!$I$6/(219453+Misc!$I$6)+14250)+20140))*(5/Misc!$L$22))-0.02</f>
         <v>3.9308479046436471</v>
@@ -12228,7 +12223,7 @@
         <f>((Misc!$J$28*(222547*Misc!$J$6/(222547+Misc!$J$6)+15750)/((222547*Misc!$J$6/(222547+Misc!$J$6)+15750)+19860))*(5/Misc!$L$22))+0.02</f>
         <v>4.0863153688422091</v>
       </c>
-      <c r="AN60" s="117"/>
+      <c r="AN60" s="99"/>
       <c r="AO60" s="14">
         <f>((Misc!$J$28*(219453*Misc!$I$6/(219453+Misc!$I$6)+14250)/((219453*Misc!$I$6/(219453+Misc!$I$6)+14250)+20140))*(5/Misc!$L$19))-0.02</f>
         <v>3.9308479046436471</v>
@@ -12408,7 +12403,7 @@
         <f>((Misc!$K$28*(222547*Misc!$J$6/(222547+Misc!$J$6)+15750)/((222547*Misc!$J$6/(222547+Misc!$J$6)+15750)+19860))*(5/Misc!$L$21))+0.02</f>
         <v>4.1272239741625532</v>
       </c>
-      <c r="AK61" s="117"/>
+      <c r="AK61" s="99"/>
       <c r="AL61" s="14">
         <f>((Misc!$K$28*(219453*Misc!$I$6/(219453+Misc!$I$6)+14250)/((219453*Misc!$I$6/(219453+Misc!$I$6)+14250)+20140))*(5/Misc!$L$22))-0.02</f>
         <v>3.9705948654549506</v>
@@ -12417,7 +12412,7 @@
         <f>((Misc!$K$28*(222547*Misc!$J$6/(222547+Misc!$J$6)+15750)/((222547*Misc!$J$6/(222547+Misc!$J$6)+15750)+19860))*(5/Misc!$L$22))+0.02</f>
         <v>4.1272239741625532</v>
       </c>
-      <c r="AN61" s="117"/>
+      <c r="AN61" s="99"/>
       <c r="AO61" s="14">
         <f>((Misc!$K$28*(219453*Misc!$I$6/(219453+Misc!$I$6)+14250)/((219453*Misc!$I$6/(219453+Misc!$I$6)+14250)+20140))*(5/Misc!$L$19))-0.02</f>
         <v>3.9705948654549506</v>
@@ -12515,10 +12510,10 @@
       <c r="AH62" s="16"/>
       <c r="AI62" s="14"/>
       <c r="AJ62" s="14"/>
-      <c r="AK62" s="118"/>
+      <c r="AK62" s="100"/>
       <c r="AL62" s="14"/>
       <c r="AM62" s="14"/>
-      <c r="AN62" s="117"/>
+      <c r="AN62" s="99"/>
       <c r="AO62" s="14"/>
       <c r="AP62" s="14"/>
       <c r="AQ62" s="15"/>
@@ -12538,7 +12533,7 @@
       <c r="BE62" s="14"/>
     </row>
     <row r="63" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="39">
+      <c r="A63" s="37">
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
@@ -12662,27 +12657,27 @@
         <f>($AH$63*5/Misc!$L$21)+0.015</f>
         <v>2.5150000000000001</v>
       </c>
-      <c r="AK63" s="117">
+      <c r="AK63" s="99">
         <v>2.4750000000000001</v>
       </c>
       <c r="AL63" s="14">
-        <f>($AK$63*5/Misc!$L$22)-0.015</f>
-        <v>2.46</v>
+        <f>($AK$63*5/Misc!$L$22)-0.015-0.1</f>
+        <v>2.36</v>
       </c>
       <c r="AM63" s="14">
-        <f>($AK$63*5/Misc!$L$22)+0.015</f>
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="AN63" s="117">
+        <f>($AK$63*5/Misc!$L$22)+0.015+0.1</f>
+        <v>2.5900000000000003</v>
+      </c>
+      <c r="AN63" s="99">
         <v>2.4750000000000001</v>
       </c>
       <c r="AO63" s="14">
-        <f>(AN63*5/Misc!$L$19)-0.015</f>
-        <v>2.46</v>
+        <f>(AN63*5/Misc!$L$19)-0.015-0.1</f>
+        <v>2.36</v>
       </c>
       <c r="AP63" s="14">
-        <f>(AN63*5/Misc!$L$19)+0.015</f>
-        <v>2.4900000000000002</v>
+        <f>(AN63*5/Misc!$L$19)+0.015+0.1</f>
+        <v>2.5900000000000003</v>
       </c>
       <c r="AQ63" s="15">
         <v>2.4900000000000002</v>
@@ -12741,7 +12736,7 @@
       </c>
     </row>
     <row r="64" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="39">
+      <c r="A64" s="37">
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
@@ -12865,27 +12860,27 @@
         <f>($AH$64*5/Misc!$L$21)+0.015</f>
         <v>2.5150000000000001</v>
       </c>
-      <c r="AK64" s="117">
+      <c r="AK64" s="99">
         <v>2.4790000000000001</v>
       </c>
       <c r="AL64" s="14">
-        <f>($AK$64*5/Misc!$L$22)-0.015</f>
-        <v>2.464</v>
+        <f>($AK$64*5/Misc!$L$22)-0.015-0.1</f>
+        <v>2.3639999999999999</v>
       </c>
       <c r="AM64" s="14">
-        <f>($AK$64*5/Misc!$L$22)+0.015</f>
-        <v>2.4940000000000002</v>
-      </c>
-      <c r="AN64" s="117">
+        <f>($AK$64*5/Misc!$L$22)+0.015+0.1</f>
+        <v>2.5940000000000003</v>
+      </c>
+      <c r="AN64" s="99">
         <v>2.4790000000000001</v>
       </c>
       <c r="AO64" s="14">
-        <f>(AN64*5/Misc!$L$19)-0.015</f>
-        <v>2.464</v>
+        <f>(AN64*5/Misc!$L$19)-0.015-0.1</f>
+        <v>2.3639999999999999</v>
       </c>
       <c r="AP64" s="14">
-        <f>(AN64*5/Misc!$L$19)+0.015</f>
-        <v>2.4940000000000002</v>
+        <f>(AN64*5/Misc!$L$19)+0.015+0.1</f>
+        <v>2.5940000000000003</v>
       </c>
       <c r="AQ64" s="15">
         <v>2.4950000000000001</v>
@@ -12986,10 +12981,10 @@
       <c r="AH65" s="16"/>
       <c r="AI65" s="14"/>
       <c r="AJ65" s="14"/>
-      <c r="AK65" s="118"/>
+      <c r="AK65" s="100"/>
       <c r="AL65" s="14"/>
       <c r="AM65" s="14"/>
-      <c r="AN65" s="117"/>
+      <c r="AN65" s="99"/>
       <c r="AO65" s="14"/>
       <c r="AP65" s="14"/>
       <c r="AQ65" s="15"/>
@@ -13133,18 +13128,18 @@
         <f>($AH$66)*(5*1.074/Misc!$L$21)+0.02*4.13</f>
         <v>12.970600000000001</v>
       </c>
-      <c r="AK66" s="117">
+      <c r="AK66" s="99">
         <v>12</v>
       </c>
-      <c r="AL66" s="43">
+      <c r="AL66" s="41">
         <f>($AK$66)*(5*0.9258/Misc!$L$22)-0.02*4.13</f>
         <v>11.027000000000001</v>
       </c>
-      <c r="AM66" s="43">
+      <c r="AM66" s="41">
         <f>($AK$66)*(5*1.074/Misc!$L$22)+0.02*4.13</f>
         <v>12.970600000000001</v>
       </c>
-      <c r="AN66" s="117">
+      <c r="AN66" s="99">
         <v>12</v>
       </c>
       <c r="AO66" s="14">
@@ -13336,18 +13331,18 @@
         <f>($AH$67)*(5*1.074/Misc!$L$21)+0.02*4.13</f>
         <v>12.970600000000001</v>
       </c>
-      <c r="AK67" s="117">
+      <c r="AK67" s="99">
         <v>12</v>
       </c>
-      <c r="AL67" s="43">
+      <c r="AL67" s="41">
         <f>($AK$67)*(5*0.9258/Misc!$L$22)-0.02*4.13</f>
         <v>11.027000000000001</v>
       </c>
-      <c r="AM67" s="43">
+      <c r="AM67" s="41">
         <f>($AK$67)*(5*1.074/Misc!$L$22)+0.02*4.13</f>
         <v>12.970600000000001</v>
       </c>
-      <c r="AN67" s="117">
+      <c r="AN67" s="99">
         <v>12</v>
       </c>
       <c r="AO67" s="14">
@@ -13457,10 +13452,10 @@
       <c r="AH68" s="16"/>
       <c r="AI68" s="14"/>
       <c r="AJ68" s="14"/>
-      <c r="AK68" s="118"/>
+      <c r="AK68" s="100"/>
       <c r="AL68" s="14"/>
       <c r="AM68" s="14"/>
-      <c r="AN68" s="117"/>
+      <c r="AN68" s="99"/>
       <c r="AO68" s="14"/>
       <c r="AP68" s="14"/>
       <c r="AQ68" s="15"/>
@@ -13604,7 +13599,7 @@
         <f>($AH$69*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK69" s="118">
+      <c r="AK69" s="100">
         <v>2.5</v>
       </c>
       <c r="AL69" s="14">
@@ -13615,7 +13610,7 @@
         <f>($AK$69*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN69" s="117">
+      <c r="AN69" s="99">
         <v>2.5</v>
       </c>
       <c r="AO69" s="14">
@@ -13807,7 +13802,7 @@
         <f>($AH$70*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK70" s="118">
+      <c r="AK70" s="100">
         <v>2.5</v>
       </c>
       <c r="AL70" s="14">
@@ -13818,7 +13813,7 @@
         <f>($AK$70*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN70" s="117">
+      <c r="AN70" s="99">
         <v>2.5</v>
       </c>
       <c r="AO70" s="14">
@@ -13928,10 +13923,10 @@
       <c r="AH71" s="16"/>
       <c r="AI71" s="14"/>
       <c r="AJ71" s="14"/>
-      <c r="AK71" s="118"/>
+      <c r="AK71" s="100"/>
       <c r="AL71" s="14"/>
       <c r="AM71" s="14"/>
-      <c r="AN71" s="117"/>
+      <c r="AN71" s="99"/>
       <c r="AO71" s="14"/>
       <c r="AP71" s="14"/>
       <c r="AQ71" s="15"/>
@@ -14075,7 +14070,7 @@
         <f>($AH$72*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK72" s="118">
+      <c r="AK72" s="100">
         <v>2.5</v>
       </c>
       <c r="AL72" s="14">
@@ -14086,7 +14081,7 @@
         <f>($AK$72*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN72" s="117">
+      <c r="AN72" s="99">
         <v>2.5</v>
       </c>
       <c r="AO72" s="14">
@@ -14278,7 +14273,7 @@
         <f>($AH$73*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AK73" s="118">
+      <c r="AK73" s="100">
         <v>2.5</v>
       </c>
       <c r="AL73" s="14">
@@ -14289,7 +14284,7 @@
         <f>($AK$73*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN73" s="117">
+      <c r="AN73" s="99">
         <v>2.5</v>
       </c>
       <c r="AO73" s="14">
@@ -14399,10 +14394,10 @@
       <c r="AH74" s="16"/>
       <c r="AI74" s="14"/>
       <c r="AJ74" s="14"/>
-      <c r="AK74" s="118"/>
+      <c r="AK74" s="100"/>
       <c r="AL74" s="14"/>
       <c r="AM74" s="14"/>
-      <c r="AN74" s="117"/>
+      <c r="AN74" s="99"/>
       <c r="AO74" s="14"/>
       <c r="AP74" s="14"/>
       <c r="AQ74" s="15"/>
@@ -14538,15 +14533,15 @@
       <c r="AH75" s="16">
         <v>2.4131333333333331</v>
       </c>
-      <c r="AI75" s="43">
+      <c r="AI75" s="41">
         <f>($AH$75*5*0.93058/Misc!$L$21)-0.015*3.4</f>
         <v>2.1946136173333328</v>
       </c>
-      <c r="AJ75" s="43">
+      <c r="AJ75" s="41">
         <f>($AH$75*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.6378789333333335</v>
       </c>
-      <c r="AK75" s="118">
+      <c r="AK75" s="100">
         <v>2.5</v>
       </c>
       <c r="AL75" s="14">
@@ -14557,7 +14552,7 @@
         <f>($AK$75*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN75" s="117">
+      <c r="AN75" s="99">
         <v>2.5</v>
       </c>
       <c r="AO75" s="14">
@@ -14741,15 +14736,15 @@
       <c r="AH76" s="16">
         <v>2.4719166666666657</v>
       </c>
-      <c r="AI76" s="43">
+      <c r="AI76" s="41">
         <f>($AH$76*5*0.93058/Misc!$L$21)-0.015*3.4</f>
         <v>2.2493162116666654</v>
       </c>
-      <c r="AJ76" s="43">
+      <c r="AJ76" s="41">
         <f>($AH$76*5*1.072/Misc!$L$21)+0.015*3.4</f>
         <v>2.7008946666666658</v>
       </c>
-      <c r="AK76" s="118">
+      <c r="AK76" s="100">
         <v>2.5</v>
       </c>
       <c r="AL76" s="14">
@@ -14760,7 +14755,7 @@
         <f>($AK$76*5*1.072/Misc!$L$22)+0.015*3.4</f>
         <v>2.7310000000000003</v>
       </c>
-      <c r="AN76" s="117">
+      <c r="AN76" s="99">
         <v>2.5</v>
       </c>
       <c r="AO76" s="14">
@@ -14868,12 +14863,12 @@
       <c r="AF77" s="14"/>
       <c r="AG77" s="14"/>
       <c r="AH77" s="16"/>
-      <c r="AI77" s="43"/>
-      <c r="AJ77" s="43"/>
-      <c r="AK77" s="118"/>
+      <c r="AI77" s="41"/>
+      <c r="AJ77" s="41"/>
+      <c r="AK77" s="100"/>
       <c r="AL77" s="14"/>
       <c r="AM77" s="14"/>
-      <c r="AN77" s="117"/>
+      <c r="AN77" s="99"/>
       <c r="AO77" s="14"/>
       <c r="AP77" s="14"/>
       <c r="AQ77" s="15"/>
@@ -14893,7 +14888,7 @@
       <c r="BE77" s="14"/>
     </row>
     <row r="78" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="39">
+      <c r="A78" s="37">
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
@@ -15009,15 +15004,15 @@
       <c r="AH78" s="16">
         <v>10.95913333333333</v>
       </c>
-      <c r="AI78" s="43">
+      <c r="AI78" s="41">
         <f>(($AH$78)*(5*0.92/Misc!$L$21)-0.02*3.75)-0.65</f>
         <v>9.3574026666666654</v>
       </c>
-      <c r="AJ78" s="43">
+      <c r="AJ78" s="41">
         <f>(($AH$78)*(5*1.08/Misc!$L$21)+0.02*3.75)-0.65</f>
         <v>11.260863999999996</v>
       </c>
-      <c r="AK78" s="118">
+      <c r="AK78" s="100">
         <v>11</v>
       </c>
       <c r="AL78" s="14">
@@ -15028,7 +15023,7 @@
         <f>(($AK$78)*(5*1.08/Misc!$L$22)+0.02*3.75)-0.65</f>
         <v>11.305</v>
       </c>
-      <c r="AN78" s="117">
+      <c r="AN78" s="99">
         <v>10.6</v>
       </c>
       <c r="AO78" s="14">
@@ -15096,7 +15091,7 @@
       </c>
     </row>
     <row r="79" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="39">
+      <c r="A79" s="37">
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
@@ -15212,15 +15207,15 @@
       <c r="AH79" s="16">
         <v>11.024400000000002</v>
       </c>
-      <c r="AI79" s="43">
+      <c r="AI79" s="41">
         <f>(($AH$79)*(5*0.92/Misc!$L$21)-0.02*3.75)-0.65</f>
         <v>9.4174480000000038</v>
       </c>
-      <c r="AJ79" s="43">
+      <c r="AJ79" s="41">
         <f>(($AH$79)*(5*1.08/Misc!$L$21)+0.02*3.75)-0.65</f>
         <v>11.331352000000001</v>
       </c>
-      <c r="AK79" s="118">
+      <c r="AK79" s="100">
         <v>11.5</v>
       </c>
       <c r="AL79" s="14">
@@ -15231,7 +15226,7 @@
         <f>(($AK$79)*(5*1.08/Misc!$L$22)+0.02*3.75)-0.65</f>
         <v>11.845000000000001</v>
       </c>
-      <c r="AN79" s="117">
+      <c r="AN79" s="99">
         <v>11.2</v>
       </c>
       <c r="AO79" s="14">
@@ -15341,10 +15336,10 @@
       <c r="AH80" s="16"/>
       <c r="AI80" s="14"/>
       <c r="AJ80" s="14"/>
-      <c r="AK80" s="118"/>
+      <c r="AK80" s="100"/>
       <c r="AL80" s="14"/>
       <c r="AM80" s="14"/>
-      <c r="AN80" s="117"/>
+      <c r="AN80" s="99"/>
       <c r="AO80" s="14"/>
       <c r="AP80" s="14"/>
       <c r="AQ80" s="15"/>
@@ -15488,7 +15483,7 @@
         <f>(Misc!$H$21*5*1.012/Misc!$L$21)+0.02*13.41</f>
         <v>48.844200000000001</v>
       </c>
-      <c r="AK81" s="118">
+      <c r="AK81" s="100">
         <v>48</v>
       </c>
       <c r="AL81" s="14">
@@ -15499,7 +15494,7 @@
         <f>(Misc!$H$22*5*1.012/Misc!$L$22)+0.02*13.41</f>
         <v>48.844200000000001</v>
       </c>
-      <c r="AN81" s="117"/>
+      <c r="AN81" s="99"/>
       <c r="AO81" s="14">
         <f>(Misc!$H$19*5*0.987/Misc!$L$19)-0.02*13.41</f>
         <v>47.107799999999997</v>
@@ -15679,7 +15674,7 @@
         <f>(Misc!$I$21*5*1.012/Misc!$L$21)+0.02*13.41</f>
         <v>48.844200000000001</v>
       </c>
-      <c r="AK82" s="118">
+      <c r="AK82" s="100">
         <v>48</v>
       </c>
       <c r="AL82" s="14">
@@ -15690,7 +15685,7 @@
         <f>(Misc!$I$22*5*1.012/Misc!$L$22)+0.02*13.41</f>
         <v>48.844200000000001</v>
       </c>
-      <c r="AN82" s="117"/>
+      <c r="AN82" s="99"/>
       <c r="AO82" s="14">
         <f>(Misc!$I$19*5*0.987/Misc!$L$19)-0.02*13.41</f>
         <v>47.107799999999997</v>
@@ -15788,10 +15783,10 @@
       <c r="AH83" s="16"/>
       <c r="AI83" s="14"/>
       <c r="AJ83" s="14"/>
-      <c r="AK83" s="118"/>
+      <c r="AK83" s="100"/>
       <c r="AL83" s="14"/>
       <c r="AM83" s="14"/>
-      <c r="AN83" s="117"/>
+      <c r="AN83" s="99"/>
       <c r="AO83" s="14"/>
       <c r="AP83" s="14"/>
       <c r="AQ83" s="15"/>
@@ -15935,7 +15930,7 @@
         <f>(Misc!$J$28)*(5*1.008/Misc!$L$21)+0.02*1.1</f>
         <v>5.0317600000000002</v>
       </c>
-      <c r="AK84" s="118">
+      <c r="AK84" s="100">
         <v>4.544299999999998</v>
       </c>
       <c r="AL84" s="14">
@@ -15946,7 +15941,7 @@
         <f>(Misc!$J$28)*(5*1.008/Misc!$L$22)+0.02*1.1</f>
         <v>5.0317600000000002</v>
       </c>
-      <c r="AN84" s="117"/>
+      <c r="AN84" s="99"/>
       <c r="AO84" s="14">
         <f>(Misc!$J$28)*(5*0.99/Misc!$L$19)-0.02*1.1</f>
         <v>4.8982999999999999</v>
@@ -16126,7 +16121,7 @@
         <f>(Misc!$K$28)*(5*1.008/Misc!$L$21)+0.02*1.1</f>
         <v>5.08216</v>
       </c>
-      <c r="AK85" s="118">
+      <c r="AK85" s="100">
         <v>4.5478500000000004</v>
       </c>
       <c r="AL85" s="14">
@@ -16137,7 +16132,7 @@
         <f>(Misc!$K$28)*(5*1.008/Misc!$L$22)+0.02*1.1</f>
         <v>5.08216</v>
       </c>
-      <c r="AN85" s="117"/>
+      <c r="AN85" s="99"/>
       <c r="AO85" s="14">
         <f>(Misc!$K$28)*(5*0.99/Misc!$L$19)-0.02*1.1</f>
         <v>4.9477999999999991</v>
@@ -16235,10 +16230,10 @@
       <c r="AH86" s="16"/>
       <c r="AI86" s="14"/>
       <c r="AJ86" s="14"/>
-      <c r="AK86" s="118"/>
+      <c r="AK86" s="100"/>
       <c r="AL86" s="14"/>
       <c r="AM86" s="14"/>
-      <c r="AN86" s="117"/>
+      <c r="AN86" s="99"/>
       <c r="AO86" s="14"/>
       <c r="AP86" s="14"/>
       <c r="AQ86" s="15"/>
@@ -16382,7 +16377,7 @@
         <f>($AH$87*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK87" s="118">
+      <c r="AK87" s="100">
         <v>2.5</v>
       </c>
       <c r="AL87" s="14">
@@ -16393,7 +16388,7 @@
         <f>($AK$87*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN87" s="117">
+      <c r="AN87" s="99">
         <v>2.5</v>
       </c>
       <c r="AO87" s="14">
@@ -16585,7 +16580,7 @@
         <f>($AH$88*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK88" s="118">
+      <c r="AK88" s="100">
         <v>2.5</v>
       </c>
       <c r="AL88" s="14">
@@ -16596,7 +16591,7 @@
         <f>($AK$88*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN88" s="117">
+      <c r="AN88" s="99">
         <v>2.5</v>
       </c>
       <c r="AO88" s="14">
@@ -16706,10 +16701,10 @@
       <c r="AH89" s="16"/>
       <c r="AI89" s="14"/>
       <c r="AJ89" s="14"/>
-      <c r="AK89" s="118"/>
+      <c r="AK89" s="100"/>
       <c r="AL89" s="14"/>
       <c r="AM89" s="14"/>
-      <c r="AN89" s="117"/>
+      <c r="AN89" s="99"/>
       <c r="AO89" s="14"/>
       <c r="AP89" s="14"/>
       <c r="AQ89" s="15"/>
@@ -16853,7 +16848,7 @@
         <f>($AH$90*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK90" s="118">
+      <c r="AK90" s="100">
         <v>2.5</v>
       </c>
       <c r="AL90" s="14">
@@ -16864,7 +16859,7 @@
         <f>($AK$90*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN90" s="117">
+      <c r="AN90" s="99">
         <v>2.5</v>
       </c>
       <c r="AO90" s="14">
@@ -17056,7 +17051,7 @@
         <f>($AH$91*5*1.072/Misc!$L$21)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AK91" s="118">
+      <c r="AK91" s="100">
         <v>2.5</v>
       </c>
       <c r="AL91" s="14">
@@ -17067,7 +17062,7 @@
         <f>($AK$91*5*1.072/Misc!$L$22)+0.02*3.4</f>
         <v>2.7480000000000002</v>
       </c>
-      <c r="AN91" s="117">
+      <c r="AN91" s="99">
         <v>2.5</v>
       </c>
       <c r="AO91" s="14">
@@ -17177,10 +17172,10 @@
       <c r="AH92" s="16"/>
       <c r="AI92" s="14"/>
       <c r="AJ92" s="14"/>
-      <c r="AK92" s="118"/>
+      <c r="AK92" s="100"/>
       <c r="AL92" s="14"/>
       <c r="AM92" s="14"/>
-      <c r="AN92" s="117"/>
+      <c r="AN92" s="99"/>
       <c r="AO92" s="14"/>
       <c r="AP92" s="14"/>
       <c r="AQ92" s="15"/>
@@ -17200,7 +17195,7 @@
       <c r="BE92" s="14"/>
     </row>
     <row r="93" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="39">
+      <c r="A93" s="37">
         <v>92</v>
       </c>
       <c r="B93" s="21" t="s">
@@ -17324,27 +17319,27 @@
         <f>($AH$93*5/Misc!$L$21)+0.08</f>
         <v>1.53</v>
       </c>
-      <c r="AK93" s="117">
+      <c r="AK93" s="99">
         <v>1.446</v>
       </c>
       <c r="AL93" s="14">
-        <f>($AK$93*5/Misc!$L$22)-0.08</f>
-        <v>1.3659999999999999</v>
+        <f>($AK$93*5/Misc!$L$22)-0.08-0.1</f>
+        <v>1.2659999999999998</v>
       </c>
       <c r="AM93" s="14">
-        <f>($AK$93*5/Misc!$L$22)+0.08</f>
-        <v>1.526</v>
-      </c>
-      <c r="AN93" s="117">
+        <f>($AK$93*5/Misc!$L$22)+0.08+0.1</f>
+        <v>1.6260000000000001</v>
+      </c>
+      <c r="AN93" s="99">
         <v>1.446</v>
       </c>
       <c r="AO93" s="14">
-        <f>(AN93*5/Misc!$L$19)-0.08</f>
-        <v>1.3659999999999999</v>
+        <f>(AN93*5/Misc!$L$19)-0.08-0.1</f>
+        <v>1.2659999999999998</v>
       </c>
       <c r="AP93" s="14">
-        <f>(AN93*5/Misc!$L$19)+0.08</f>
-        <v>1.526</v>
+        <f>(AN93*5/Misc!$L$19)+0.08+0.1</f>
+        <v>1.6260000000000001</v>
       </c>
       <c r="AQ93" s="15">
         <v>1.5449999999999999</v>
@@ -17403,7 +17398,7 @@
       </c>
     </row>
     <row r="94" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="39">
+      <c r="A94" s="37">
         <v>93</v>
       </c>
       <c r="B94" s="21" t="s">
@@ -17527,27 +17522,27 @@
         <f>($AH$94*5/Misc!$L$21)+0.08</f>
         <v>1.61</v>
       </c>
-      <c r="AK94" s="117">
+      <c r="AK94" s="99">
         <v>1.4910000000000001</v>
       </c>
       <c r="AL94" s="14">
-        <f>($AK$94*5/Misc!$L$22)-0.08</f>
-        <v>1.411</v>
+        <f>($AK$94*5/Misc!$L$22)-0.08-0.1</f>
+        <v>1.3109999999999999</v>
       </c>
       <c r="AM94" s="14">
-        <f>($AK$94*5/Misc!$L$22)+0.08</f>
-        <v>1.5710000000000002</v>
-      </c>
-      <c r="AN94" s="117">
+        <f>($AK$94*5/Misc!$L$22)+0.08+0.1</f>
+        <v>1.6710000000000003</v>
+      </c>
+      <c r="AN94" s="99">
         <v>1.4910000000000001</v>
       </c>
       <c r="AO94" s="14">
-        <f>(AN94*5/Misc!$L$19)-0.08</f>
-        <v>1.411</v>
+        <f>(AN94*5/Misc!$L$19)-0.08-0.1</f>
+        <v>1.3109999999999999</v>
       </c>
       <c r="AP94" s="14">
-        <f>(AN94*5/Misc!$L$19)+0.08</f>
-        <v>1.5710000000000002</v>
+        <f>(AN94*5/Misc!$L$19)+0.08+0.1</f>
+        <v>1.6710000000000003</v>
       </c>
       <c r="AQ94" s="15">
         <v>1.5629999999999999</v>
@@ -17648,10 +17643,10 @@
       <c r="AH95" s="15"/>
       <c r="AI95" s="14"/>
       <c r="AJ95" s="14"/>
-      <c r="AK95" s="118"/>
+      <c r="AK95" s="100"/>
       <c r="AL95" s="14"/>
       <c r="AM95" s="14"/>
-      <c r="AN95" s="117"/>
+      <c r="AN95" s="99"/>
       <c r="AO95" s="14"/>
       <c r="AP95" s="14"/>
       <c r="AQ95" s="15"/>
@@ -17735,12 +17730,12 @@
       </c>
       <c r="AI96" s="14"/>
       <c r="AJ96" s="14"/>
-      <c r="AK96" s="117">
+      <c r="AK96" s="99">
         <v>160</v>
       </c>
       <c r="AL96" s="14"/>
       <c r="AM96" s="14"/>
-      <c r="AN96" s="117">
+      <c r="AN96" s="99">
         <v>160</v>
       </c>
       <c r="AO96" s="14"/>
@@ -17836,12 +17831,12 @@
       </c>
       <c r="AI97" s="14"/>
       <c r="AJ97" s="14"/>
-      <c r="AK97" s="117">
+      <c r="AK97" s="99">
         <v>1</v>
       </c>
       <c r="AL97" s="14"/>
       <c r="AM97" s="14"/>
-      <c r="AN97" s="117">
+      <c r="AN97" s="99">
         <v>1</v>
       </c>
       <c r="AO97" s="14"/>
@@ -17937,12 +17932,12 @@
       </c>
       <c r="AI98" s="14"/>
       <c r="AJ98" s="14"/>
-      <c r="AK98" s="117">
+      <c r="AK98" s="99">
         <v>0</v>
       </c>
       <c r="AL98" s="14"/>
       <c r="AM98" s="14"/>
-      <c r="AN98" s="117">
+      <c r="AN98" s="99">
         <v>0</v>
       </c>
       <c r="AO98" s="14"/>
@@ -18038,12 +18033,12 @@
       </c>
       <c r="AI99" s="14"/>
       <c r="AJ99" s="14"/>
-      <c r="AK99" s="117">
+      <c r="AK99" s="99">
         <v>1</v>
       </c>
       <c r="AL99" s="14"/>
       <c r="AM99" s="14"/>
-      <c r="AN99" s="117">
+      <c r="AN99" s="99">
         <v>1</v>
       </c>
       <c r="AO99" s="14"/>
@@ -18139,12 +18134,12 @@
       </c>
       <c r="AI100" s="14"/>
       <c r="AJ100" s="14"/>
-      <c r="AK100" s="117">
+      <c r="AK100" s="99">
         <v>0</v>
       </c>
       <c r="AL100" s="14"/>
       <c r="AM100" s="14"/>
-      <c r="AN100" s="117">
+      <c r="AN100" s="99">
         <v>0</v>
       </c>
       <c r="AO100" s="14"/>
@@ -18240,12 +18235,12 @@
       </c>
       <c r="AI101" s="14"/>
       <c r="AJ101" s="14"/>
-      <c r="AK101" s="117">
+      <c r="AK101" s="99">
         <v>1</v>
       </c>
       <c r="AL101" s="14"/>
       <c r="AM101" s="14"/>
-      <c r="AN101" s="117">
+      <c r="AN101" s="99">
         <v>1</v>
       </c>
       <c r="AO101" s="14"/>
@@ -18341,12 +18336,12 @@
       </c>
       <c r="AI102" s="14"/>
       <c r="AJ102" s="14"/>
-      <c r="AK102" s="117">
+      <c r="AK102" s="99">
         <v>0</v>
       </c>
       <c r="AL102" s="14"/>
       <c r="AM102" s="14"/>
-      <c r="AN102" s="117">
+      <c r="AN102" s="99">
         <v>0</v>
       </c>
       <c r="AO102" s="14"/>
@@ -18442,12 +18437,12 @@
       </c>
       <c r="AI103" s="14"/>
       <c r="AJ103" s="14"/>
-      <c r="AK103" s="117">
+      <c r="AK103" s="99">
         <v>1</v>
       </c>
       <c r="AL103" s="14"/>
       <c r="AM103" s="14"/>
-      <c r="AN103" s="117">
+      <c r="AN103" s="99">
         <v>1</v>
       </c>
       <c r="AO103" s="14"/>
@@ -18543,12 +18538,12 @@
       </c>
       <c r="AI104" s="14"/>
       <c r="AJ104" s="14"/>
-      <c r="AK104" s="117">
+      <c r="AK104" s="99">
         <v>0</v>
       </c>
       <c r="AL104" s="14"/>
       <c r="AM104" s="14"/>
-      <c r="AN104" s="117">
+      <c r="AN104" s="99">
         <v>0</v>
       </c>
       <c r="AO104" s="14"/>
@@ -18644,12 +18639,12 @@
       </c>
       <c r="AI105" s="14"/>
       <c r="AJ105" s="14"/>
-      <c r="AK105" s="117">
+      <c r="AK105" s="99">
         <v>1</v>
       </c>
       <c r="AL105" s="14"/>
       <c r="AM105" s="14"/>
-      <c r="AN105" s="117">
+      <c r="AN105" s="99">
         <v>1</v>
       </c>
       <c r="AO105" s="14"/>
@@ -18745,12 +18740,12 @@
       </c>
       <c r="AI106" s="14"/>
       <c r="AJ106" s="14"/>
-      <c r="AK106" s="117">
+      <c r="AK106" s="99">
         <v>0</v>
       </c>
       <c r="AL106" s="14"/>
       <c r="AM106" s="14"/>
-      <c r="AN106" s="117">
+      <c r="AN106" s="99">
         <v>0</v>
       </c>
       <c r="AO106" s="14"/>
@@ -18846,12 +18841,12 @@
       </c>
       <c r="AI107" s="14"/>
       <c r="AJ107" s="14"/>
-      <c r="AK107" s="119">
+      <c r="AK107" s="101">
         <v>160</v>
       </c>
       <c r="AL107" s="14"/>
       <c r="AM107" s="14"/>
-      <c r="AN107" s="117">
+      <c r="AN107" s="99">
         <v>160</v>
       </c>
       <c r="AO107" s="14"/>
@@ -18883,7 +18878,7 @@
       <c r="BE107" s="14"/>
     </row>
     <row r="108" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="39">
+      <c r="A108" s="37">
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
@@ -19007,18 +19002,18 @@
         <f>$AH$108+8</f>
         <v>1008</v>
       </c>
-      <c r="AK108" s="117">
+      <c r="AK108" s="99">
         <v>1000</v>
       </c>
-      <c r="AL108" s="84">
+      <c r="AL108" s="80">
         <f>$AK$108-8</f>
         <v>992</v>
       </c>
-      <c r="AM108" s="84">
+      <c r="AM108" s="80">
         <f>$AK$108+8</f>
         <v>1008</v>
       </c>
-      <c r="AN108" s="117">
+      <c r="AN108" s="99">
         <v>1000</v>
       </c>
       <c r="AO108" s="14">
@@ -19086,7 +19081,7 @@
       </c>
     </row>
     <row r="109" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="39">
+      <c r="A109" s="37">
         <v>108</v>
       </c>
       <c r="B109" s="11" t="s">
@@ -19210,18 +19205,18 @@
         <f>$AH$109+8</f>
         <v>1008</v>
       </c>
-      <c r="AK109" s="117">
+      <c r="AK109" s="99">
         <v>1000</v>
       </c>
-      <c r="AL109" s="84">
+      <c r="AL109" s="80">
         <f>$AK$109-8</f>
         <v>992</v>
       </c>
-      <c r="AM109" s="84">
+      <c r="AM109" s="80">
         <f>$AK$109+8</f>
         <v>1008</v>
       </c>
-      <c r="AN109" s="117">
+      <c r="AN109" s="99">
         <v>1000</v>
       </c>
       <c r="AO109" s="14">
@@ -19289,7 +19284,7 @@
       </c>
     </row>
     <row r="110" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="39">
+      <c r="A110" s="37">
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
@@ -19413,18 +19408,18 @@
         <f>$AH$110+8</f>
         <v>508</v>
       </c>
-      <c r="AK110" s="117">
+      <c r="AK110" s="99">
         <v>500</v>
       </c>
-      <c r="AL110" s="84">
+      <c r="AL110" s="80">
         <f>$AK$110-8</f>
         <v>492</v>
       </c>
-      <c r="AM110" s="84">
+      <c r="AM110" s="80">
         <f>$AK$110+8</f>
         <v>508</v>
       </c>
-      <c r="AN110" s="117">
+      <c r="AN110" s="99">
         <v>496</v>
       </c>
       <c r="AO110" s="14">
@@ -19492,7 +19487,7 @@
       </c>
     </row>
     <row r="111" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="39">
+      <c r="A111" s="37">
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
@@ -19616,18 +19611,18 @@
         <f>$AH$111+8</f>
         <v>508</v>
       </c>
-      <c r="AK111" s="117">
+      <c r="AK111" s="99">
         <v>500</v>
       </c>
-      <c r="AL111" s="84">
+      <c r="AL111" s="80">
         <f>$AK$111-8</f>
         <v>492</v>
       </c>
-      <c r="AM111" s="84">
+      <c r="AM111" s="80">
         <f>$AK$111+8</f>
         <v>508</v>
       </c>
-      <c r="AN111" s="117">
+      <c r="AN111" s="99">
         <v>497</v>
       </c>
       <c r="AO111" s="14">
@@ -19739,10 +19734,10 @@
       <c r="AH112" s="15"/>
       <c r="AI112" s="14"/>
       <c r="AJ112" s="14"/>
-      <c r="AK112" s="118"/>
+      <c r="AK112" s="100"/>
       <c r="AL112" s="14"/>
       <c r="AM112" s="14"/>
-      <c r="AN112" s="117"/>
+      <c r="AN112" s="99"/>
       <c r="AO112" s="14"/>
       <c r="AP112" s="14"/>
       <c r="AQ112" s="15"/>
@@ -19826,12 +19821,12 @@
       </c>
       <c r="AI113" s="14"/>
       <c r="AJ113" s="14"/>
-      <c r="AK113" s="117">
+      <c r="AK113" s="99">
         <v>160</v>
       </c>
       <c r="AL113" s="14"/>
       <c r="AM113" s="14"/>
-      <c r="AN113" s="117">
+      <c r="AN113" s="99">
         <v>160</v>
       </c>
       <c r="AO113" s="14"/>
@@ -19927,12 +19922,12 @@
       </c>
       <c r="AI114" s="14"/>
       <c r="AJ114" s="14"/>
-      <c r="AK114" s="117">
+      <c r="AK114" s="99">
         <v>135</v>
       </c>
       <c r="AL114" s="14"/>
       <c r="AM114" s="14"/>
-      <c r="AN114" s="117">
+      <c r="AN114" s="99">
         <v>135</v>
       </c>
       <c r="AO114" s="14"/>
@@ -20048,14 +20043,14 @@
       <c r="AJ115" s="14">
         <v>-81</v>
       </c>
-      <c r="AK115" s="118"/>
+      <c r="AK115" s="100"/>
       <c r="AL115" s="14">
         <v>-206</v>
       </c>
       <c r="AM115" s="14">
         <v>-81</v>
       </c>
-      <c r="AN115" s="117"/>
+      <c r="AN115" s="99"/>
       <c r="AO115" s="14">
         <v>-206</v>
       </c>
@@ -20183,14 +20178,14 @@
       <c r="AJ116" s="14">
         <v>1600</v>
       </c>
-      <c r="AK116" s="118"/>
+      <c r="AK116" s="100"/>
       <c r="AL116" s="14">
         <v>-1600</v>
       </c>
       <c r="AM116" s="14">
         <v>1600</v>
       </c>
-      <c r="AN116" s="117"/>
+      <c r="AN116" s="99"/>
       <c r="AO116" s="14">
         <v>-1600</v>
       </c>
@@ -20318,14 +20313,14 @@
       <c r="AJ117" s="14">
         <v>207</v>
       </c>
-      <c r="AK117" s="118"/>
+      <c r="AK117" s="100"/>
       <c r="AL117" s="14">
         <v>78</v>
       </c>
       <c r="AM117" s="14">
         <v>207</v>
       </c>
-      <c r="AN117" s="117"/>
+      <c r="AN117" s="99"/>
       <c r="AO117" s="14">
         <v>78</v>
       </c>
@@ -20453,14 +20448,14 @@
       <c r="AJ118" s="14">
         <v>1600</v>
       </c>
-      <c r="AK118" s="118"/>
+      <c r="AK118" s="100"/>
       <c r="AL118" s="14">
         <v>-1600</v>
       </c>
       <c r="AM118" s="14">
         <v>1600</v>
       </c>
-      <c r="AN118" s="117"/>
+      <c r="AN118" s="99"/>
       <c r="AO118" s="14">
         <v>-1600</v>
       </c>
@@ -20588,14 +20583,14 @@
       <c r="AJ119" s="14">
         <v>-120</v>
       </c>
-      <c r="AK119" s="118"/>
+      <c r="AK119" s="100"/>
       <c r="AL119" s="14">
         <v>-727</v>
       </c>
       <c r="AM119" s="14">
         <v>-120</v>
       </c>
-      <c r="AN119" s="117"/>
+      <c r="AN119" s="99"/>
       <c r="AO119" s="14">
         <v>-727</v>
       </c>
@@ -20723,14 +20718,14 @@
       <c r="AJ120" s="14">
         <v>1600</v>
       </c>
-      <c r="AK120" s="118"/>
+      <c r="AK120" s="100"/>
       <c r="AL120" s="14">
         <v>-1600</v>
       </c>
       <c r="AM120" s="14">
         <v>1600</v>
       </c>
-      <c r="AN120" s="117"/>
+      <c r="AN120" s="99"/>
       <c r="AO120" s="14">
         <v>-1600</v>
       </c>
@@ -20898,7 +20893,7 @@
         <f>255*0.001</f>
         <v>0.255</v>
       </c>
-      <c r="AK121" s="117">
+      <c r="AK121" s="99">
         <v>0</v>
       </c>
       <c r="AL121" s="14">
@@ -20909,7 +20904,7 @@
         <f>255*0.001</f>
         <v>0.255</v>
       </c>
-      <c r="AN121" s="117">
+      <c r="AN121" s="99">
         <v>0</v>
       </c>
       <c r="AO121" s="14">
@@ -21101,7 +21096,7 @@
         <f>255*0.001</f>
         <v>0.255</v>
       </c>
-      <c r="AK122" s="117">
+      <c r="AK122" s="99">
         <v>0</v>
       </c>
       <c r="AL122" s="14">
@@ -21112,7 +21107,7 @@
         <f>255*0.001</f>
         <v>0.255</v>
       </c>
-      <c r="AN122" s="117">
+      <c r="AN122" s="99">
         <v>0</v>
       </c>
       <c r="AO122" s="14">
@@ -21304,7 +21299,7 @@
         <f>-395*0.001</f>
         <v>-0.39500000000000002</v>
       </c>
-      <c r="AK123" s="117">
+      <c r="AK123" s="99">
         <v>1</v>
       </c>
       <c r="AL123" s="14">
@@ -21315,7 +21310,7 @@
         <f>-395*0.001</f>
         <v>-0.39500000000000002</v>
       </c>
-      <c r="AN123" s="117">
+      <c r="AN123" s="99">
         <v>-1</v>
       </c>
       <c r="AO123" s="14">
@@ -21447,12 +21442,12 @@
       </c>
       <c r="AI124" s="14"/>
       <c r="AJ124" s="14"/>
-      <c r="AK124" s="117">
+      <c r="AK124" s="99">
         <v>35327</v>
       </c>
       <c r="AL124" s="14"/>
       <c r="AM124" s="14"/>
-      <c r="AN124" s="117">
+      <c r="AN124" s="99">
         <v>35327</v>
       </c>
       <c r="AO124" s="14"/>
@@ -21548,12 +21543,12 @@
       </c>
       <c r="AI125" s="14"/>
       <c r="AJ125" s="14"/>
-      <c r="AK125" s="117">
+      <c r="AK125" s="99">
         <v>137</v>
       </c>
       <c r="AL125" s="14"/>
       <c r="AM125" s="14"/>
-      <c r="AN125" s="117">
+      <c r="AN125" s="99">
         <v>137</v>
       </c>
       <c r="AO125" s="14"/>
@@ -21649,12 +21644,12 @@
       </c>
       <c r="AI126" s="14"/>
       <c r="AJ126" s="14"/>
-      <c r="AK126" s="117">
+      <c r="AK126" s="99">
         <v>255</v>
       </c>
       <c r="AL126" s="14"/>
       <c r="AM126" s="14"/>
-      <c r="AN126" s="117">
+      <c r="AN126" s="99">
         <v>255</v>
       </c>
       <c r="AO126" s="14"/>
@@ -21750,12 +21745,12 @@
       </c>
       <c r="AI127" s="14"/>
       <c r="AJ127" s="14"/>
-      <c r="AK127" s="117">
+      <c r="AK127" s="99">
         <v>4096</v>
       </c>
       <c r="AL127" s="14"/>
       <c r="AM127" s="14"/>
-      <c r="AN127" s="117">
+      <c r="AN127" s="99">
         <v>4096</v>
       </c>
       <c r="AO127" s="14"/>
@@ -21851,12 +21846,12 @@
       </c>
       <c r="AI128" s="14"/>
       <c r="AJ128" s="14"/>
-      <c r="AK128" s="117">
+      <c r="AK128" s="99">
         <v>0</v>
       </c>
       <c r="AL128" s="14"/>
       <c r="AM128" s="14"/>
-      <c r="AN128" s="117">
+      <c r="AN128" s="99">
         <v>0</v>
       </c>
       <c r="AO128" s="14"/>
@@ -21952,12 +21947,12 @@
       </c>
       <c r="AI129" s="14"/>
       <c r="AJ129" s="14"/>
-      <c r="AK129" s="117">
+      <c r="AK129" s="99">
         <v>0</v>
       </c>
       <c r="AL129" s="14"/>
       <c r="AM129" s="14"/>
-      <c r="AN129" s="117">
+      <c r="AN129" s="99">
         <v>0</v>
       </c>
       <c r="AO129" s="14"/>
@@ -22053,12 +22048,12 @@
       </c>
       <c r="AI130" s="14"/>
       <c r="AJ130" s="14"/>
-      <c r="AK130" s="117">
+      <c r="AK130" s="99">
         <v>2</v>
       </c>
       <c r="AL130" s="14"/>
       <c r="AM130" s="14"/>
-      <c r="AN130" s="117">
+      <c r="AN130" s="99">
         <v>2</v>
       </c>
       <c r="AO130" s="14"/>
@@ -22154,12 +22149,12 @@
       </c>
       <c r="AI131" s="14"/>
       <c r="AJ131" s="14"/>
-      <c r="AK131" s="117">
+      <c r="AK131" s="99">
         <v>0</v>
       </c>
       <c r="AL131" s="14"/>
       <c r="AM131" s="14"/>
-      <c r="AN131" s="117">
+      <c r="AN131" s="99">
         <v>0</v>
       </c>
       <c r="AO131" s="14"/>
@@ -22255,12 +22250,12 @@
       </c>
       <c r="AI132" s="14"/>
       <c r="AJ132" s="14"/>
-      <c r="AK132" s="117">
+      <c r="AK132" s="99">
         <v>0</v>
       </c>
       <c r="AL132" s="14"/>
       <c r="AM132" s="14"/>
-      <c r="AN132" s="117">
+      <c r="AN132" s="99">
         <v>0</v>
       </c>
       <c r="AO132" s="14"/>
@@ -22356,12 +22351,12 @@
       </c>
       <c r="AI133" s="14"/>
       <c r="AJ133" s="14"/>
-      <c r="AK133" s="117">
+      <c r="AK133" s="99">
         <v>0</v>
       </c>
       <c r="AL133" s="14"/>
       <c r="AM133" s="14"/>
-      <c r="AN133" s="117">
+      <c r="AN133" s="99">
         <v>0</v>
       </c>
       <c r="AO133" s="14"/>
@@ -22457,12 +22452,12 @@
       </c>
       <c r="AI134" s="14"/>
       <c r="AJ134" s="14"/>
-      <c r="AK134" s="117">
+      <c r="AK134" s="99">
         <v>160</v>
       </c>
       <c r="AL134" s="14"/>
       <c r="AM134" s="14"/>
-      <c r="AN134" s="117">
+      <c r="AN134" s="99">
         <v>160</v>
       </c>
       <c r="AO134" s="14"/>
@@ -22558,12 +22553,12 @@
       </c>
       <c r="AI135" s="14"/>
       <c r="AJ135" s="14"/>
-      <c r="AK135" s="117">
+      <c r="AK135" s="99">
         <v>1</v>
       </c>
       <c r="AL135" s="14"/>
       <c r="AM135" s="14"/>
-      <c r="AN135" s="117">
+      <c r="AN135" s="99">
         <v>1</v>
       </c>
       <c r="AO135" s="14"/>
@@ -22659,12 +22654,12 @@
       </c>
       <c r="AI136" s="14"/>
       <c r="AJ136" s="14"/>
-      <c r="AK136" s="117">
+      <c r="AK136" s="99">
         <v>160</v>
       </c>
       <c r="AL136" s="14"/>
       <c r="AM136" s="14"/>
-      <c r="AN136" s="117">
+      <c r="AN136" s="99">
         <v>160</v>
       </c>
       <c r="AO136" s="14"/>
@@ -22760,12 +22755,12 @@
       </c>
       <c r="AI137" s="14"/>
       <c r="AJ137" s="14"/>
-      <c r="AK137" s="117">
+      <c r="AK137" s="99">
         <v>129</v>
       </c>
       <c r="AL137" s="14"/>
       <c r="AM137" s="14"/>
-      <c r="AN137" s="117">
+      <c r="AN137" s="99">
         <v>129</v>
       </c>
       <c r="AO137" s="14"/>
@@ -22861,12 +22856,12 @@
       </c>
       <c r="AI138" s="14"/>
       <c r="AJ138" s="14"/>
-      <c r="AK138" s="117">
+      <c r="AK138" s="99">
         <v>1</v>
       </c>
       <c r="AL138" s="14"/>
       <c r="AM138" s="14"/>
-      <c r="AN138" s="117">
+      <c r="AN138" s="99">
         <v>1</v>
       </c>
       <c r="AO138" s="14"/>
@@ -22962,12 +22957,12 @@
       </c>
       <c r="AI139" s="14"/>
       <c r="AJ139" s="14"/>
-      <c r="AK139" s="117">
+      <c r="AK139" s="99">
         <v>0</v>
       </c>
       <c r="AL139" s="14"/>
       <c r="AM139" s="14"/>
-      <c r="AN139" s="117">
+      <c r="AN139" s="99">
         <v>0</v>
       </c>
       <c r="AO139" s="14"/>
@@ -23063,12 +23058,12 @@
       </c>
       <c r="AI140" s="14"/>
       <c r="AJ140" s="14"/>
-      <c r="AK140" s="117">
+      <c r="AK140" s="99">
         <v>0</v>
       </c>
       <c r="AL140" s="14"/>
       <c r="AM140" s="14"/>
-      <c r="AN140" s="117">
+      <c r="AN140" s="99">
         <v>0</v>
       </c>
       <c r="AO140" s="14"/>
@@ -23164,12 +23159,12 @@
       </c>
       <c r="AI141" s="14"/>
       <c r="AJ141" s="14"/>
-      <c r="AK141" s="117">
+      <c r="AK141" s="99">
         <v>0</v>
       </c>
       <c r="AL141" s="14"/>
       <c r="AM141" s="14"/>
-      <c r="AN141" s="117">
+      <c r="AN141" s="99">
         <v>0</v>
       </c>
       <c r="AO141" s="14"/>
@@ -23265,12 +23260,12 @@
       </c>
       <c r="AI142" s="14"/>
       <c r="AJ142" s="14"/>
-      <c r="AK142" s="117">
+      <c r="AK142" s="99">
         <v>0</v>
       </c>
       <c r="AL142" s="14"/>
       <c r="AM142" s="14"/>
-      <c r="AN142" s="117">
+      <c r="AN142" s="99">
         <v>0</v>
       </c>
       <c r="AO142" s="14"/>
@@ -23366,12 +23361,12 @@
       </c>
       <c r="AI143" s="14"/>
       <c r="AJ143" s="14"/>
-      <c r="AK143" s="117">
+      <c r="AK143" s="99">
         <v>0</v>
       </c>
       <c r="AL143" s="14"/>
       <c r="AM143" s="14"/>
-      <c r="AN143" s="117">
+      <c r="AN143" s="99">
         <v>0</v>
       </c>
       <c r="AO143" s="14"/>
@@ -23467,12 +23462,12 @@
       </c>
       <c r="AI144" s="14"/>
       <c r="AJ144" s="14"/>
-      <c r="AK144" s="117">
+      <c r="AK144" s="99">
         <v>0</v>
       </c>
       <c r="AL144" s="14"/>
       <c r="AM144" s="14"/>
-      <c r="AN144" s="117">
+      <c r="AN144" s="99">
         <v>0</v>
       </c>
       <c r="AO144" s="14"/>
@@ -23568,12 +23563,12 @@
       </c>
       <c r="AI145" s="14"/>
       <c r="AJ145" s="14"/>
-      <c r="AK145" s="117">
+      <c r="AK145" s="99">
         <v>1</v>
       </c>
       <c r="AL145" s="14"/>
       <c r="AM145" s="14"/>
-      <c r="AN145" s="117">
+      <c r="AN145" s="99">
         <v>1</v>
       </c>
       <c r="AO145" s="14"/>
@@ -23669,12 +23664,12 @@
       </c>
       <c r="AI146" s="14"/>
       <c r="AJ146" s="14"/>
-      <c r="AK146" s="117">
+      <c r="AK146" s="99">
         <v>0</v>
       </c>
       <c r="AL146" s="14"/>
       <c r="AM146" s="14"/>
-      <c r="AN146" s="117">
+      <c r="AN146" s="99">
         <v>0</v>
       </c>
       <c r="AO146" s="14"/>
@@ -23770,12 +23765,12 @@
       </c>
       <c r="AI147" s="14"/>
       <c r="AJ147" s="14"/>
-      <c r="AK147" s="117">
+      <c r="AK147" s="99">
         <v>0</v>
       </c>
       <c r="AL147" s="14"/>
       <c r="AM147" s="14"/>
-      <c r="AN147" s="117">
+      <c r="AN147" s="99">
         <v>0</v>
       </c>
       <c r="AO147" s="14"/>
@@ -23871,12 +23866,12 @@
       </c>
       <c r="AI148" s="14"/>
       <c r="AJ148" s="14"/>
-      <c r="AK148" s="117">
+      <c r="AK148" s="99">
         <v>0</v>
       </c>
       <c r="AL148" s="14"/>
       <c r="AM148" s="14"/>
-      <c r="AN148" s="117">
+      <c r="AN148" s="99">
         <v>0</v>
       </c>
       <c r="AO148" s="14"/>
@@ -23972,12 +23967,12 @@
       </c>
       <c r="AI149" s="14"/>
       <c r="AJ149" s="14"/>
-      <c r="AK149" s="117">
+      <c r="AK149" s="99">
         <v>0</v>
       </c>
       <c r="AL149" s="14"/>
       <c r="AM149" s="14"/>
-      <c r="AN149" s="117">
+      <c r="AN149" s="99">
         <v>0</v>
       </c>
       <c r="AO149" s="14"/>
@@ -24073,12 +24068,12 @@
       </c>
       <c r="AI150" s="14"/>
       <c r="AJ150" s="14"/>
-      <c r="AK150" s="117">
+      <c r="AK150" s="99">
         <v>0</v>
       </c>
       <c r="AL150" s="14"/>
       <c r="AM150" s="14"/>
-      <c r="AN150" s="117">
+      <c r="AN150" s="99">
         <v>0</v>
       </c>
       <c r="AO150" s="14"/>
@@ -24174,12 +24169,12 @@
       </c>
       <c r="AI151" s="14"/>
       <c r="AJ151" s="14"/>
-      <c r="AK151" s="117">
+      <c r="AK151" s="99">
         <v>0</v>
       </c>
       <c r="AL151" s="14"/>
       <c r="AM151" s="14"/>
-      <c r="AN151" s="117">
+      <c r="AN151" s="99">
         <v>0</v>
       </c>
       <c r="AO151" s="14"/>
@@ -24275,12 +24270,12 @@
       </c>
       <c r="AI152" s="14"/>
       <c r="AJ152" s="14"/>
-      <c r="AK152" s="117">
+      <c r="AK152" s="99">
         <v>0</v>
       </c>
       <c r="AL152" s="14"/>
       <c r="AM152" s="14"/>
-      <c r="AN152" s="117">
+      <c r="AN152" s="99">
         <v>0</v>
       </c>
       <c r="AO152" s="14"/>
@@ -24376,12 +24371,12 @@
       </c>
       <c r="AI153" s="14"/>
       <c r="AJ153" s="14"/>
-      <c r="AK153" s="117">
+      <c r="AK153" s="99">
         <v>0</v>
       </c>
       <c r="AL153" s="14"/>
       <c r="AM153" s="14"/>
-      <c r="AN153" s="117">
+      <c r="AN153" s="99">
         <v>0</v>
       </c>
       <c r="AO153" s="14"/>
@@ -24477,12 +24472,12 @@
       </c>
       <c r="AI154" s="14"/>
       <c r="AJ154" s="14"/>
-      <c r="AK154" s="117">
+      <c r="AK154" s="99">
         <v>0</v>
       </c>
       <c r="AL154" s="14"/>
       <c r="AM154" s="14"/>
-      <c r="AN154" s="117">
+      <c r="AN154" s="99">
         <v>0</v>
       </c>
       <c r="AO154" s="14"/>
@@ -24578,12 +24573,12 @@
       </c>
       <c r="AI155" s="14"/>
       <c r="AJ155" s="14"/>
-      <c r="AK155" s="117">
+      <c r="AK155" s="99">
         <v>0</v>
       </c>
       <c r="AL155" s="14"/>
       <c r="AM155" s="14"/>
-      <c r="AN155" s="117">
+      <c r="AN155" s="99">
         <v>0</v>
       </c>
       <c r="AO155" s="14"/>
@@ -24679,12 +24674,12 @@
       </c>
       <c r="AI156" s="14"/>
       <c r="AJ156" s="14"/>
-      <c r="AK156" s="117">
+      <c r="AK156" s="99">
         <v>0</v>
       </c>
       <c r="AL156" s="14"/>
       <c r="AM156" s="14"/>
-      <c r="AN156" s="117">
+      <c r="AN156" s="99">
         <v>0</v>
       </c>
       <c r="AO156" s="14"/>
@@ -24780,12 +24775,12 @@
       </c>
       <c r="AI157" s="14"/>
       <c r="AJ157" s="14"/>
-      <c r="AK157" s="117">
+      <c r="AK157" s="99">
         <v>0</v>
       </c>
       <c r="AL157" s="14"/>
       <c r="AM157" s="14"/>
-      <c r="AN157" s="117">
+      <c r="AN157" s="99">
         <v>0</v>
       </c>
       <c r="AO157" s="14"/>
@@ -24881,12 +24876,12 @@
       </c>
       <c r="AI158" s="14"/>
       <c r="AJ158" s="14"/>
-      <c r="AK158" s="117">
+      <c r="AK158" s="99">
         <v>0</v>
       </c>
       <c r="AL158" s="14"/>
       <c r="AM158" s="14"/>
-      <c r="AN158" s="117">
+      <c r="AN158" s="99">
         <v>0</v>
       </c>
       <c r="AO158" s="14"/>
@@ -24982,12 +24977,12 @@
       </c>
       <c r="AI159" s="14"/>
       <c r="AJ159" s="14"/>
-      <c r="AK159" s="117">
+      <c r="AK159" s="99">
         <v>0</v>
       </c>
       <c r="AL159" s="14"/>
       <c r="AM159" s="14"/>
-      <c r="AN159" s="117">
+      <c r="AN159" s="99">
         <v>0</v>
       </c>
       <c r="AO159" s="14"/>
@@ -25083,12 +25078,12 @@
       </c>
       <c r="AI160" s="14"/>
       <c r="AJ160" s="14"/>
-      <c r="AK160" s="117">
+      <c r="AK160" s="99">
         <v>0</v>
       </c>
       <c r="AL160" s="14"/>
       <c r="AM160" s="14"/>
-      <c r="AN160" s="117">
+      <c r="AN160" s="99">
         <v>0</v>
       </c>
       <c r="AO160" s="14"/>
@@ -25184,12 +25179,12 @@
       </c>
       <c r="AI161" s="14"/>
       <c r="AJ161" s="14"/>
-      <c r="AK161" s="117">
+      <c r="AK161" s="99">
         <v>0</v>
       </c>
       <c r="AL161" s="14"/>
       <c r="AM161" s="14"/>
-      <c r="AN161" s="117">
+      <c r="AN161" s="99">
         <v>0</v>
       </c>
       <c r="AO161" s="14"/>
@@ -25285,12 +25280,12 @@
       </c>
       <c r="AI162" s="14"/>
       <c r="AJ162" s="14"/>
-      <c r="AK162" s="117">
+      <c r="AK162" s="99">
         <v>0</v>
       </c>
       <c r="AL162" s="14"/>
       <c r="AM162" s="14"/>
-      <c r="AN162" s="117">
+      <c r="AN162" s="99">
         <v>0</v>
       </c>
       <c r="AO162" s="14"/>
@@ -25386,12 +25381,12 @@
       </c>
       <c r="AI163" s="14"/>
       <c r="AJ163" s="14"/>
-      <c r="AK163" s="117">
+      <c r="AK163" s="99">
         <v>0</v>
       </c>
       <c r="AL163" s="14"/>
       <c r="AM163" s="14"/>
-      <c r="AN163" s="117">
+      <c r="AN163" s="99">
         <v>0</v>
       </c>
       <c r="AO163" s="14"/>
@@ -25487,12 +25482,12 @@
       </c>
       <c r="AI164" s="14"/>
       <c r="AJ164" s="14"/>
-      <c r="AK164" s="117">
+      <c r="AK164" s="99">
         <v>0</v>
       </c>
       <c r="AL164" s="14"/>
       <c r="AM164" s="14"/>
-      <c r="AN164" s="117">
+      <c r="AN164" s="99">
         <v>0</v>
       </c>
       <c r="AO164" s="14"/>
@@ -25588,12 +25583,12 @@
       </c>
       <c r="AI165" s="14"/>
       <c r="AJ165" s="14"/>
-      <c r="AK165" s="117">
+      <c r="AK165" s="99">
         <v>0</v>
       </c>
       <c r="AL165" s="14"/>
       <c r="AM165" s="14"/>
-      <c r="AN165" s="117">
+      <c r="AN165" s="99">
         <v>0</v>
       </c>
       <c r="AO165" s="14"/>
@@ -25689,12 +25684,12 @@
       </c>
       <c r="AI166" s="14"/>
       <c r="AJ166" s="14"/>
-      <c r="AK166" s="117">
+      <c r="AK166" s="99">
         <v>0</v>
       </c>
       <c r="AL166" s="14"/>
       <c r="AM166" s="14"/>
-      <c r="AN166" s="117">
+      <c r="AN166" s="99">
         <v>0</v>
       </c>
       <c r="AO166" s="14"/>
@@ -25790,12 +25785,12 @@
       </c>
       <c r="AI167" s="14"/>
       <c r="AJ167" s="14"/>
-      <c r="AK167" s="117">
+      <c r="AK167" s="99">
         <v>0</v>
       </c>
       <c r="AL167" s="14"/>
       <c r="AM167" s="14"/>
-      <c r="AN167" s="117">
+      <c r="AN167" s="99">
         <v>0</v>
       </c>
       <c r="AO167" s="14"/>
@@ -25891,12 +25886,12 @@
       </c>
       <c r="AI168" s="14"/>
       <c r="AJ168" s="14"/>
-      <c r="AK168" s="117">
+      <c r="AK168" s="99">
         <v>0</v>
       </c>
       <c r="AL168" s="14"/>
       <c r="AM168" s="14"/>
-      <c r="AN168" s="117">
+      <c r="AN168" s="99">
         <v>0</v>
       </c>
       <c r="AO168" s="14"/>
@@ -25992,12 +25987,12 @@
       </c>
       <c r="AI169" s="14"/>
       <c r="AJ169" s="14"/>
-      <c r="AK169" s="117">
+      <c r="AK169" s="99">
         <v>0</v>
       </c>
       <c r="AL169" s="14"/>
       <c r="AM169" s="14"/>
-      <c r="AN169" s="117">
+      <c r="AN169" s="99">
         <v>0</v>
       </c>
       <c r="AO169" s="14"/>
@@ -26093,12 +26088,12 @@
       </c>
       <c r="AI170" s="14"/>
       <c r="AJ170" s="14"/>
-      <c r="AK170" s="117">
+      <c r="AK170" s="99">
         <v>0</v>
       </c>
       <c r="AL170" s="14"/>
       <c r="AM170" s="14"/>
-      <c r="AN170" s="117">
+      <c r="AN170" s="99">
         <v>0</v>
       </c>
       <c r="AO170" s="14"/>
@@ -26194,12 +26189,12 @@
       </c>
       <c r="AI171" s="14"/>
       <c r="AJ171" s="14"/>
-      <c r="AK171" s="117">
+      <c r="AK171" s="99">
         <v>0</v>
       </c>
       <c r="AL171" s="14"/>
       <c r="AM171" s="14"/>
-      <c r="AN171" s="117">
+      <c r="AN171" s="99">
         <v>0</v>
       </c>
       <c r="AO171" s="14"/>
@@ -26295,12 +26290,12 @@
       </c>
       <c r="AI172" s="14"/>
       <c r="AJ172" s="14"/>
-      <c r="AK172" s="117">
+      <c r="AK172" s="99">
         <v>0</v>
       </c>
       <c r="AL172" s="14"/>
       <c r="AM172" s="14"/>
-      <c r="AN172" s="117">
+      <c r="AN172" s="99">
         <v>0</v>
       </c>
       <c r="AO172" s="14"/>
@@ -26396,12 +26391,12 @@
       </c>
       <c r="AI173" s="14"/>
       <c r="AJ173" s="14"/>
-      <c r="AK173" s="117">
+      <c r="AK173" s="99">
         <v>0</v>
       </c>
       <c r="AL173" s="14"/>
       <c r="AM173" s="14"/>
-      <c r="AN173" s="117">
+      <c r="AN173" s="99">
         <v>0</v>
       </c>
       <c r="AO173" s="14"/>
@@ -26497,12 +26492,12 @@
       </c>
       <c r="AI174" s="14"/>
       <c r="AJ174" s="14"/>
-      <c r="AK174" s="117">
+      <c r="AK174" s="99">
         <v>0</v>
       </c>
       <c r="AL174" s="14"/>
       <c r="AM174" s="14"/>
-      <c r="AN174" s="117">
+      <c r="AN174" s="99">
         <v>0</v>
       </c>
       <c r="AO174" s="14"/>
@@ -26598,12 +26593,12 @@
       </c>
       <c r="AI175" s="14"/>
       <c r="AJ175" s="14"/>
-      <c r="AK175" s="117">
+      <c r="AK175" s="99">
         <v>0</v>
       </c>
       <c r="AL175" s="14"/>
       <c r="AM175" s="14"/>
-      <c r="AN175" s="117">
+      <c r="AN175" s="99">
         <v>0</v>
       </c>
       <c r="AO175" s="14"/>
@@ -26699,12 +26694,12 @@
       </c>
       <c r="AI176" s="14"/>
       <c r="AJ176" s="14"/>
-      <c r="AK176" s="117">
+      <c r="AK176" s="99">
         <v>0</v>
       </c>
       <c r="AL176" s="14"/>
       <c r="AM176" s="14"/>
-      <c r="AN176" s="117">
+      <c r="AN176" s="99">
         <v>0</v>
       </c>
       <c r="AO176" s="14"/>
@@ -26800,12 +26795,12 @@
       </c>
       <c r="AI177" s="14"/>
       <c r="AJ177" s="14"/>
-      <c r="AK177" s="117">
+      <c r="AK177" s="99">
         <v>0</v>
       </c>
       <c r="AL177" s="14"/>
       <c r="AM177" s="14"/>
-      <c r="AN177" s="117">
+      <c r="AN177" s="99">
         <v>0</v>
       </c>
       <c r="AO177" s="14"/>
@@ -26901,12 +26896,12 @@
       </c>
       <c r="AI178" s="14"/>
       <c r="AJ178" s="14"/>
-      <c r="AK178" s="117">
+      <c r="AK178" s="99">
         <v>0</v>
       </c>
       <c r="AL178" s="14"/>
       <c r="AM178" s="14"/>
-      <c r="AN178" s="117">
+      <c r="AN178" s="99">
         <v>0</v>
       </c>
       <c r="AO178" s="14"/>
@@ -27002,12 +26997,12 @@
       </c>
       <c r="AI179" s="14"/>
       <c r="AJ179" s="14"/>
-      <c r="AK179" s="117">
+      <c r="AK179" s="99">
         <v>0</v>
       </c>
       <c r="AL179" s="14"/>
       <c r="AM179" s="14"/>
-      <c r="AN179" s="117">
+      <c r="AN179" s="99">
         <v>0</v>
       </c>
       <c r="AO179" s="14"/>
@@ -27103,12 +27098,12 @@
       </c>
       <c r="AI180" s="14"/>
       <c r="AJ180" s="14"/>
-      <c r="AK180" s="117">
+      <c r="AK180" s="99">
         <v>0</v>
       </c>
       <c r="AL180" s="14"/>
       <c r="AM180" s="14"/>
-      <c r="AN180" s="117">
+      <c r="AN180" s="99">
         <v>0</v>
       </c>
       <c r="AO180" s="14"/>
@@ -27204,12 +27199,12 @@
       </c>
       <c r="AI181" s="14"/>
       <c r="AJ181" s="14"/>
-      <c r="AK181" s="117">
+      <c r="AK181" s="99">
         <v>0</v>
       </c>
       <c r="AL181" s="14"/>
       <c r="AM181" s="14"/>
-      <c r="AN181" s="117">
+      <c r="AN181" s="99">
         <v>0</v>
       </c>
       <c r="AO181" s="14"/>
@@ -27305,12 +27300,12 @@
       </c>
       <c r="AI182" s="14"/>
       <c r="AJ182" s="14"/>
-      <c r="AK182" s="117">
+      <c r="AK182" s="99">
         <v>0</v>
       </c>
       <c r="AL182" s="14"/>
       <c r="AM182" s="14"/>
-      <c r="AN182" s="117">
+      <c r="AN182" s="99">
         <v>0</v>
       </c>
       <c r="AO182" s="14"/>
@@ -27406,12 +27401,12 @@
       </c>
       <c r="AI183" s="14"/>
       <c r="AJ183" s="14"/>
-      <c r="AK183" s="117">
+      <c r="AK183" s="99">
         <v>0</v>
       </c>
       <c r="AL183" s="14"/>
       <c r="AM183" s="14"/>
-      <c r="AN183" s="117">
+      <c r="AN183" s="99">
         <v>0</v>
       </c>
       <c r="AO183" s="14"/>
@@ -27507,12 +27502,12 @@
       </c>
       <c r="AI184" s="14"/>
       <c r="AJ184" s="14"/>
-      <c r="AK184" s="117">
+      <c r="AK184" s="99">
         <v>0</v>
       </c>
       <c r="AL184" s="14"/>
       <c r="AM184" s="14"/>
-      <c r="AN184" s="117">
+      <c r="AN184" s="99">
         <v>0</v>
       </c>
       <c r="AO184" s="14"/>
@@ -27608,12 +27603,12 @@
       </c>
       <c r="AI185" s="14"/>
       <c r="AJ185" s="14"/>
-      <c r="AK185" s="117">
+      <c r="AK185" s="99">
         <v>0</v>
       </c>
       <c r="AL185" s="14"/>
       <c r="AM185" s="14"/>
-      <c r="AN185" s="117">
+      <c r="AN185" s="99">
         <v>0</v>
       </c>
       <c r="AO185" s="14"/>
@@ -27709,12 +27704,12 @@
       </c>
       <c r="AI186" s="14"/>
       <c r="AJ186" s="14"/>
-      <c r="AK186" s="117">
+      <c r="AK186" s="99">
         <v>0</v>
       </c>
       <c r="AL186" s="14"/>
       <c r="AM186" s="14"/>
-      <c r="AN186" s="117">
+      <c r="AN186" s="99">
         <v>0</v>
       </c>
       <c r="AO186" s="14"/>
@@ -27810,12 +27805,12 @@
       </c>
       <c r="AI187" s="14"/>
       <c r="AJ187" s="14"/>
-      <c r="AK187" s="117">
+      <c r="AK187" s="99">
         <v>0</v>
       </c>
       <c r="AL187" s="14"/>
       <c r="AM187" s="14"/>
-      <c r="AN187" s="117">
+      <c r="AN187" s="99">
         <v>0</v>
       </c>
       <c r="AO187" s="14"/>
@@ -27911,12 +27906,12 @@
       </c>
       <c r="AI188" s="14"/>
       <c r="AJ188" s="14"/>
-      <c r="AK188" s="117">
+      <c r="AK188" s="99">
         <v>0</v>
       </c>
       <c r="AL188" s="14"/>
       <c r="AM188" s="14"/>
-      <c r="AN188" s="117">
+      <c r="AN188" s="99">
         <v>0</v>
       </c>
       <c r="AO188" s="14"/>
@@ -28012,12 +28007,12 @@
       </c>
       <c r="AI189" s="14"/>
       <c r="AJ189" s="14"/>
-      <c r="AK189" s="117">
+      <c r="AK189" s="99">
         <v>0</v>
       </c>
       <c r="AL189" s="14"/>
       <c r="AM189" s="14"/>
-      <c r="AN189" s="117">
+      <c r="AN189" s="99">
         <v>0</v>
       </c>
       <c r="AO189" s="14"/>
@@ -28113,12 +28108,12 @@
       </c>
       <c r="AI190" s="14"/>
       <c r="AJ190" s="14"/>
-      <c r="AK190" s="117">
+      <c r="AK190" s="99">
         <v>0</v>
       </c>
       <c r="AL190" s="14"/>
       <c r="AM190" s="14"/>
-      <c r="AN190" s="117">
+      <c r="AN190" s="99">
         <v>0</v>
       </c>
       <c r="AO190" s="14"/>
@@ -28214,12 +28209,12 @@
       </c>
       <c r="AI191" s="14"/>
       <c r="AJ191" s="14"/>
-      <c r="AK191" s="117">
+      <c r="AK191" s="99">
         <v>0</v>
       </c>
       <c r="AL191" s="14"/>
       <c r="AM191" s="14"/>
-      <c r="AN191" s="117">
+      <c r="AN191" s="99">
         <v>0</v>
       </c>
       <c r="AO191" s="14"/>
@@ -28315,12 +28310,12 @@
       </c>
       <c r="AI192" s="14"/>
       <c r="AJ192" s="14"/>
-      <c r="AK192" s="117">
+      <c r="AK192" s="99">
         <v>0</v>
       </c>
       <c r="AL192" s="14"/>
       <c r="AM192" s="14"/>
-      <c r="AN192" s="117">
+      <c r="AN192" s="99">
         <v>0</v>
       </c>
       <c r="AO192" s="14"/>
@@ -28416,12 +28411,12 @@
       </c>
       <c r="AI193" s="14"/>
       <c r="AJ193" s="14"/>
-      <c r="AK193" s="117">
+      <c r="AK193" s="99">
         <v>0</v>
       </c>
       <c r="AL193" s="14"/>
       <c r="AM193" s="14"/>
-      <c r="AN193" s="117">
+      <c r="AN193" s="99">
         <v>0</v>
       </c>
       <c r="AO193" s="14"/>
@@ -28517,12 +28512,12 @@
       </c>
       <c r="AI194" s="14"/>
       <c r="AJ194" s="14"/>
-      <c r="AK194" s="117">
+      <c r="AK194" s="99">
         <v>0</v>
       </c>
       <c r="AL194" s="14"/>
       <c r="AM194" s="14"/>
-      <c r="AN194" s="117">
+      <c r="AN194" s="99">
         <v>0</v>
       </c>
       <c r="AO194" s="14"/>
@@ -28618,12 +28613,12 @@
       </c>
       <c r="AI195" s="14"/>
       <c r="AJ195" s="14"/>
-      <c r="AK195" s="117">
+      <c r="AK195" s="99">
         <v>0</v>
       </c>
       <c r="AL195" s="14"/>
       <c r="AM195" s="14"/>
-      <c r="AN195" s="117">
+      <c r="AN195" s="99">
         <v>0</v>
       </c>
       <c r="AO195" s="14"/>
@@ -28719,12 +28714,12 @@
       </c>
       <c r="AI196" s="14"/>
       <c r="AJ196" s="14"/>
-      <c r="AK196" s="117">
+      <c r="AK196" s="99">
         <v>0</v>
       </c>
       <c r="AL196" s="14"/>
       <c r="AM196" s="14"/>
-      <c r="AN196" s="117">
+      <c r="AN196" s="99">
         <v>0</v>
       </c>
       <c r="AO196" s="14"/>
@@ -28820,12 +28815,12 @@
       </c>
       <c r="AI197" s="14"/>
       <c r="AJ197" s="14"/>
-      <c r="AK197" s="117">
+      <c r="AK197" s="99">
         <v>0</v>
       </c>
       <c r="AL197" s="14"/>
       <c r="AM197" s="14"/>
-      <c r="AN197" s="117">
+      <c r="AN197" s="99">
         <v>0</v>
       </c>
       <c r="AO197" s="14"/>
@@ -28921,12 +28916,12 @@
       </c>
       <c r="AI198" s="14"/>
       <c r="AJ198" s="14"/>
-      <c r="AK198" s="117">
+      <c r="AK198" s="99">
         <v>0</v>
       </c>
       <c r="AL198" s="14"/>
       <c r="AM198" s="14"/>
-      <c r="AN198" s="117">
+      <c r="AN198" s="99">
         <v>0</v>
       </c>
       <c r="AO198" s="14"/>
@@ -29022,12 +29017,12 @@
       </c>
       <c r="AI199" s="14"/>
       <c r="AJ199" s="14"/>
-      <c r="AK199" s="117">
+      <c r="AK199" s="99">
         <v>0</v>
       </c>
       <c r="AL199" s="14"/>
       <c r="AM199" s="14"/>
-      <c r="AN199" s="117">
+      <c r="AN199" s="99">
         <v>0</v>
       </c>
       <c r="AO199" s="14"/>
@@ -29123,12 +29118,12 @@
       </c>
       <c r="AI200" s="14"/>
       <c r="AJ200" s="14"/>
-      <c r="AK200" s="117">
+      <c r="AK200" s="99">
         <v>0</v>
       </c>
       <c r="AL200" s="14"/>
       <c r="AM200" s="14"/>
-      <c r="AN200" s="117">
+      <c r="AN200" s="99">
         <v>0</v>
       </c>
       <c r="AO200" s="14"/>
@@ -29224,12 +29219,12 @@
       </c>
       <c r="AI201" s="14"/>
       <c r="AJ201" s="14"/>
-      <c r="AK201" s="117">
+      <c r="AK201" s="99">
         <v>0</v>
       </c>
       <c r="AL201" s="14"/>
       <c r="AM201" s="14"/>
-      <c r="AN201" s="117">
+      <c r="AN201" s="99">
         <v>0</v>
       </c>
       <c r="AO201" s="14"/>
@@ -29325,12 +29320,12 @@
       </c>
       <c r="AI202" s="14"/>
       <c r="AJ202" s="14"/>
-      <c r="AK202" s="117">
+      <c r="AK202" s="99">
         <v>0</v>
       </c>
       <c r="AL202" s="14"/>
       <c r="AM202" s="14"/>
-      <c r="AN202" s="117">
+      <c r="AN202" s="99">
         <v>0</v>
       </c>
       <c r="AO202" s="14"/>
@@ -29426,12 +29421,12 @@
       </c>
       <c r="AI203" s="14"/>
       <c r="AJ203" s="14"/>
-      <c r="AK203" s="117">
+      <c r="AK203" s="99">
         <v>0</v>
       </c>
       <c r="AL203" s="14"/>
       <c r="AM203" s="14"/>
-      <c r="AN203" s="117">
+      <c r="AN203" s="99">
         <v>0</v>
       </c>
       <c r="AO203" s="14"/>
@@ -29527,12 +29522,12 @@
       </c>
       <c r="AI204" s="14"/>
       <c r="AJ204" s="14"/>
-      <c r="AK204" s="117">
+      <c r="AK204" s="99">
         <v>0</v>
       </c>
       <c r="AL204" s="14"/>
       <c r="AM204" s="14"/>
-      <c r="AN204" s="117">
+      <c r="AN204" s="99">
         <v>0</v>
       </c>
       <c r="AO204" s="14"/>
@@ -29628,12 +29623,12 @@
       </c>
       <c r="AI205" s="14"/>
       <c r="AJ205" s="14"/>
-      <c r="AK205" s="117">
+      <c r="AK205" s="99">
         <v>0</v>
       </c>
       <c r="AL205" s="14"/>
       <c r="AM205" s="14"/>
-      <c r="AN205" s="117">
+      <c r="AN205" s="99">
         <v>0</v>
       </c>
       <c r="AO205" s="14"/>
@@ -29729,12 +29724,12 @@
       </c>
       <c r="AI206" s="14"/>
       <c r="AJ206" s="14"/>
-      <c r="AK206" s="117">
+      <c r="AK206" s="99">
         <v>0</v>
       </c>
       <c r="AL206" s="14"/>
       <c r="AM206" s="14"/>
-      <c r="AN206" s="117">
+      <c r="AN206" s="99">
         <v>0</v>
       </c>
       <c r="AO206" s="14"/>
@@ -29830,12 +29825,12 @@
       </c>
       <c r="AI207" s="14"/>
       <c r="AJ207" s="14"/>
-      <c r="AK207" s="117">
+      <c r="AK207" s="99">
         <v>0</v>
       </c>
       <c r="AL207" s="14"/>
       <c r="AM207" s="14"/>
-      <c r="AN207" s="117">
+      <c r="AN207" s="99">
         <v>0</v>
       </c>
       <c r="AO207" s="14"/>
@@ -29931,12 +29926,12 @@
       </c>
       <c r="AI208" s="14"/>
       <c r="AJ208" s="14"/>
-      <c r="AK208" s="117">
+      <c r="AK208" s="99">
         <v>0</v>
       </c>
       <c r="AL208" s="14"/>
       <c r="AM208" s="14"/>
-      <c r="AN208" s="117">
+      <c r="AN208" s="99">
         <v>0</v>
       </c>
       <c r="AO208" s="14"/>
@@ -30032,12 +30027,12 @@
       </c>
       <c r="AI209" s="14"/>
       <c r="AJ209" s="14"/>
-      <c r="AK209" s="117">
+      <c r="AK209" s="99">
         <v>0</v>
       </c>
       <c r="AL209" s="14"/>
       <c r="AM209" s="14"/>
-      <c r="AN209" s="117">
+      <c r="AN209" s="99">
         <v>0</v>
       </c>
       <c r="AO209" s="14"/>
@@ -30133,12 +30128,12 @@
       </c>
       <c r="AI210" s="14"/>
       <c r="AJ210" s="14"/>
-      <c r="AK210" s="117">
+      <c r="AK210" s="99">
         <v>0</v>
       </c>
       <c r="AL210" s="14"/>
       <c r="AM210" s="14"/>
-      <c r="AN210" s="117">
+      <c r="AN210" s="99">
         <v>0</v>
       </c>
       <c r="AO210" s="14"/>
@@ -30234,12 +30229,12 @@
       </c>
       <c r="AI211" s="14"/>
       <c r="AJ211" s="14"/>
-      <c r="AK211" s="117">
+      <c r="AK211" s="99">
         <v>0</v>
       </c>
       <c r="AL211" s="14"/>
       <c r="AM211" s="14"/>
-      <c r="AN211" s="117">
+      <c r="AN211" s="99">
         <v>0</v>
       </c>
       <c r="AO211" s="14"/>
@@ -30335,12 +30330,12 @@
       </c>
       <c r="AI212" s="14"/>
       <c r="AJ212" s="14"/>
-      <c r="AK212" s="117">
+      <c r="AK212" s="99">
         <v>0</v>
       </c>
       <c r="AL212" s="14"/>
       <c r="AM212" s="14"/>
-      <c r="AN212" s="117">
+      <c r="AN212" s="99">
         <v>0</v>
       </c>
       <c r="AO212" s="14"/>
@@ -30436,12 +30431,12 @@
       </c>
       <c r="AI213" s="14"/>
       <c r="AJ213" s="14"/>
-      <c r="AK213" s="117">
+      <c r="AK213" s="99">
         <v>0</v>
       </c>
       <c r="AL213" s="14"/>
       <c r="AM213" s="14"/>
-      <c r="AN213" s="117">
+      <c r="AN213" s="99">
         <v>0</v>
       </c>
       <c r="AO213" s="14"/>
@@ -30537,12 +30532,12 @@
       </c>
       <c r="AI214" s="14"/>
       <c r="AJ214" s="14"/>
-      <c r="AK214" s="117">
+      <c r="AK214" s="99">
         <v>0</v>
       </c>
       <c r="AL214" s="14"/>
       <c r="AM214" s="14"/>
-      <c r="AN214" s="117">
+      <c r="AN214" s="99">
         <v>0</v>
       </c>
       <c r="AO214" s="14"/>
@@ -30638,12 +30633,12 @@
       </c>
       <c r="AI215" s="14"/>
       <c r="AJ215" s="14"/>
-      <c r="AK215" s="117">
+      <c r="AK215" s="99">
         <v>0</v>
       </c>
       <c r="AL215" s="14"/>
       <c r="AM215" s="14"/>
-      <c r="AN215" s="117">
+      <c r="AN215" s="99">
         <v>0</v>
       </c>
       <c r="AO215" s="14"/>
@@ -30739,12 +30734,12 @@
       </c>
       <c r="AI216" s="14"/>
       <c r="AJ216" s="14"/>
-      <c r="AK216" s="117">
+      <c r="AK216" s="99">
         <v>0</v>
       </c>
       <c r="AL216" s="14"/>
       <c r="AM216" s="14"/>
-      <c r="AN216" s="117">
+      <c r="AN216" s="99">
         <v>0</v>
       </c>
       <c r="AO216" s="14"/>
@@ -30840,12 +30835,12 @@
       </c>
       <c r="AI217" s="14"/>
       <c r="AJ217" s="14"/>
-      <c r="AK217" s="117">
+      <c r="AK217" s="99">
         <v>0</v>
       </c>
       <c r="AL217" s="14"/>
       <c r="AM217" s="14"/>
-      <c r="AN217" s="117">
+      <c r="AN217" s="99">
         <v>0</v>
       </c>
       <c r="AO217" s="14"/>
@@ -30941,12 +30936,12 @@
       </c>
       <c r="AI218" s="14"/>
       <c r="AJ218" s="14"/>
-      <c r="AK218" s="117">
+      <c r="AK218" s="99">
         <v>0</v>
       </c>
       <c r="AL218" s="14"/>
       <c r="AM218" s="14"/>
-      <c r="AN218" s="117">
+      <c r="AN218" s="99">
         <v>0</v>
       </c>
       <c r="AO218" s="14"/>
@@ -31042,12 +31037,12 @@
       </c>
       <c r="AI219" s="14"/>
       <c r="AJ219" s="14"/>
-      <c r="AK219" s="117">
+      <c r="AK219" s="99">
         <v>0</v>
       </c>
       <c r="AL219" s="14"/>
       <c r="AM219" s="14"/>
-      <c r="AN219" s="117">
+      <c r="AN219" s="99">
         <v>0</v>
       </c>
       <c r="AO219" s="14"/>
@@ -31143,12 +31138,12 @@
       </c>
       <c r="AI220" s="14"/>
       <c r="AJ220" s="14"/>
-      <c r="AK220" s="117">
+      <c r="AK220" s="99">
         <v>0</v>
       </c>
       <c r="AL220" s="14"/>
       <c r="AM220" s="14"/>
-      <c r="AN220" s="117">
+      <c r="AN220" s="99">
         <v>0</v>
       </c>
       <c r="AO220" s="14"/>
@@ -31284,7 +31279,7 @@
         <f>Misc!$F$21+3</f>
         <v>4</v>
       </c>
-      <c r="AK221" s="117"/>
+      <c r="AK221" s="99"/>
       <c r="AL221" s="14">
         <f>Misc!$F$22-3</f>
         <v>157</v>
@@ -31293,7 +31288,7 @@
         <f>Misc!$F$22+3</f>
         <v>163</v>
       </c>
-      <c r="AN221" s="117"/>
+      <c r="AN221" s="99"/>
       <c r="AO221" s="14">
         <f>Misc!$F$23-3</f>
         <v>207</v>
@@ -31453,7 +31448,7 @@
         <f>Misc!$G$21+3</f>
         <v>4</v>
       </c>
-      <c r="AK222" s="117"/>
+      <c r="AK222" s="99"/>
       <c r="AL222" s="14">
         <f>Misc!$G$22-3</f>
         <v>157</v>
@@ -31462,7 +31457,7 @@
         <f>Misc!$G$22+3</f>
         <v>163</v>
       </c>
-      <c r="AN222" s="117"/>
+      <c r="AN222" s="99"/>
       <c r="AO222" s="14">
         <f>Misc!$G$23-3</f>
         <v>207</v>
@@ -31622,7 +31617,7 @@
         <f>-(SQRT(2)*Misc!$G$21)+5</f>
         <v>3.5857864376269051</v>
       </c>
-      <c r="AK223" s="117"/>
+      <c r="AK223" s="99"/>
       <c r="AL223" s="14">
         <f>-(SQRT(2)*Misc!$G$22)-Misc!$O$22</f>
         <v>-238.27416997969522</v>
@@ -31631,14 +31626,14 @@
         <f>-(SQRT(2)*Misc!$G$22)+Misc!$O$22</f>
         <v>-214.27416997969522</v>
       </c>
-      <c r="AN223" s="117"/>
+      <c r="AN223" s="99"/>
       <c r="AO223" s="14">
         <f>-(SQRT(2)*Misc!$G$23)-Misc!$O$23</f>
-        <v>-311.98484809834997</v>
+        <v>-312.98484809834997</v>
       </c>
       <c r="AP223" s="14">
         <f>-(SQRT(2)*Misc!$G$23)+Misc!$O$23</f>
-        <v>-281.98484809834997</v>
+        <v>-280.98484809834997</v>
       </c>
       <c r="AQ223" s="15"/>
       <c r="AR223" s="14">
@@ -31687,7 +31682,7 @@
       </c>
     </row>
     <row r="224" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="39">
+      <c r="A224" s="37">
         <v>223</v>
       </c>
       <c r="B224" s="23" t="s">
@@ -31791,7 +31786,7 @@
         <f>-(SQRT(2)*Misc!$G$21)+5</f>
         <v>3.5857864376269051</v>
       </c>
-      <c r="AK224" s="117"/>
+      <c r="AK224" s="99"/>
       <c r="AL224" s="14">
         <f>-(SQRT(2)*Misc!$G$22)-Misc!$O$22</f>
         <v>-238.27416997969522</v>
@@ -31800,14 +31795,14 @@
         <f>-(SQRT(2)*Misc!$G$22)+Misc!$O$22</f>
         <v>-214.27416997969522</v>
       </c>
-      <c r="AN224" s="117"/>
+      <c r="AN224" s="99"/>
       <c r="AO224" s="14">
         <f>-(SQRT(2)*Misc!$G$23)-Misc!$O$23</f>
-        <v>-311.98484809834997</v>
+        <v>-312.98484809834997</v>
       </c>
       <c r="AP224" s="14">
         <f>-(SQRT(2)*Misc!$G$23)+Misc!$O$23</f>
-        <v>-281.98484809834997</v>
+        <v>-280.98484809834997</v>
       </c>
       <c r="AQ224" s="15"/>
       <c r="AR224" s="14">
@@ -31856,7 +31851,7 @@
       </c>
     </row>
     <row r="225" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="39">
+      <c r="A225" s="37">
         <v>224</v>
       </c>
       <c r="B225" s="23" t="s">
@@ -31960,7 +31955,7 @@
         <f>-(SQRT(2)*Misc!$G$21)+5</f>
         <v>3.5857864376269051</v>
       </c>
-      <c r="AK225" s="117"/>
+      <c r="AK225" s="99"/>
       <c r="AL225" s="14">
         <f>-(SQRT(2)*Misc!$G$22)-Misc!$O$22</f>
         <v>-238.27416997969522</v>
@@ -31969,14 +31964,14 @@
         <f>-(SQRT(2)*Misc!$G$22)+Misc!$O$22</f>
         <v>-214.27416997969522</v>
       </c>
-      <c r="AN225" s="117"/>
+      <c r="AN225" s="99"/>
       <c r="AO225" s="14">
         <f>-(SQRT(2)*Misc!$G$23)-Misc!$O$23</f>
-        <v>-311.98484809834997</v>
+        <v>-312.98484809834997</v>
       </c>
       <c r="AP225" s="14">
         <f>-(SQRT(2)*Misc!$G$23)+Misc!$O$23</f>
-        <v>-281.98484809834997</v>
+        <v>-280.98484809834997</v>
       </c>
       <c r="AQ225" s="15"/>
       <c r="AR225" s="14">
@@ -32025,7 +32020,7 @@
       </c>
     </row>
     <row r="226" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="39">
+      <c r="A226" s="37">
         <v>225</v>
       </c>
       <c r="B226" s="23" t="s">
@@ -32129,7 +32124,7 @@
         <f>(SQRT(2)*Misc!$G$21)+5</f>
         <v>6.4142135623730949</v>
       </c>
-      <c r="AK226" s="117"/>
+      <c r="AK226" s="99"/>
       <c r="AL226" s="14">
         <f>(SQRT(2)*Misc!$G$22)-Misc!$O$22</f>
         <v>214.27416997969522</v>
@@ -32138,14 +32133,14 @@
         <f>(SQRT(2)*Misc!$G$22)+Misc!$O$22</f>
         <v>238.27416997969522</v>
       </c>
-      <c r="AN226" s="117"/>
+      <c r="AN226" s="99"/>
       <c r="AO226" s="14">
-        <f>(SQRT(2)*Misc!$G$23)-5</f>
-        <v>291.98484809834997</v>
+        <f>(SQRT(2)*Misc!$G$23)-Misc!$O$23</f>
+        <v>280.98484809834997</v>
       </c>
       <c r="AP226" s="14">
         <f>(SQRT(2)*Misc!$G$23)+Misc!$O$23</f>
-        <v>311.98484809834997</v>
+        <v>312.98484809834997</v>
       </c>
       <c r="AQ226" s="15"/>
       <c r="AR226" s="14">
@@ -32194,7 +32189,7 @@
       </c>
     </row>
     <row r="227" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="39">
+      <c r="A227" s="37">
         <v>226</v>
       </c>
       <c r="B227" s="23" t="s">
@@ -32298,7 +32293,7 @@
         <f>(SQRT(2)*Misc!$G$21)+5</f>
         <v>6.4142135623730949</v>
       </c>
-      <c r="AK227" s="117"/>
+      <c r="AK227" s="99"/>
       <c r="AL227" s="14">
         <f>(SQRT(2)*Misc!$G$22)-Misc!$O$22</f>
         <v>214.27416997969522</v>
@@ -32307,14 +32302,14 @@
         <f>(SQRT(2)*Misc!$G$22)+Misc!$O$22</f>
         <v>238.27416997969522</v>
       </c>
-      <c r="AN227" s="117"/>
+      <c r="AN227" s="99"/>
       <c r="AO227" s="14">
-        <f>(SQRT(2)*Misc!$G$23)-5</f>
-        <v>291.98484809834997</v>
+        <f>(SQRT(2)*Misc!$G$23)-Misc!$O$23</f>
+        <v>280.98484809834997</v>
       </c>
       <c r="AP227" s="14">
         <f>(SQRT(2)*Misc!$G$23)+Misc!$O$23</f>
-        <v>311.98484809834997</v>
+        <v>312.98484809834997</v>
       </c>
       <c r="AQ227" s="15"/>
       <c r="AR227" s="14">
@@ -32363,7 +32358,7 @@
       </c>
     </row>
     <row r="228" spans="1:57" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="39">
+      <c r="A228" s="37">
         <v>227</v>
       </c>
       <c r="B228" s="23" t="s">
@@ -32467,7 +32462,7 @@
         <f>(SQRT(2)*Misc!$G$21)+5</f>
         <v>6.4142135623730949</v>
       </c>
-      <c r="AK228" s="117"/>
+      <c r="AK228" s="99"/>
       <c r="AL228" s="14">
         <f>(SQRT(2)*Misc!$G$22)-Misc!$O$22</f>
         <v>214.27416997969522</v>
@@ -32476,14 +32471,14 @@
         <f>(SQRT(2)*Misc!$G$22)+Misc!$O$22</f>
         <v>238.27416997969522</v>
       </c>
-      <c r="AN228" s="117"/>
+      <c r="AN228" s="99"/>
       <c r="AO228" s="14">
-        <f>(SQRT(2)*Misc!$G$23)-5</f>
-        <v>291.98484809834997</v>
+        <f>(SQRT(2)*Misc!$G$23)-Misc!$O$23</f>
+        <v>280.98484809834997</v>
       </c>
       <c r="AP228" s="14">
         <f>(SQRT(2)*Misc!$G$23)+Misc!$O$23</f>
-        <v>311.98484809834997</v>
+        <v>312.98484809834997</v>
       </c>
       <c r="AQ228" s="15"/>
       <c r="AR228" s="14">
@@ -32636,7 +32631,7 @@
         <f>Misc!$N$21</f>
         <v>110</v>
       </c>
-      <c r="AK229" s="117"/>
+      <c r="AK229" s="99"/>
       <c r="AL229" s="14">
         <f>Misc!$M$22</f>
         <v>-20</v>
@@ -32645,7 +32640,7 @@
         <f>Misc!$N$22</f>
         <v>110</v>
       </c>
-      <c r="AN229" s="117"/>
+      <c r="AN229" s="99"/>
       <c r="AO229" s="14">
         <f>Misc!$M$23</f>
         <v>-20</v>
@@ -32743,10 +32738,10 @@
       <c r="AH230" s="15"/>
       <c r="AI230" s="14"/>
       <c r="AJ230" s="14"/>
-      <c r="AK230" s="117"/>
+      <c r="AK230" s="99"/>
       <c r="AL230" s="14"/>
       <c r="AM230" s="14"/>
-      <c r="AN230" s="117"/>
+      <c r="AN230" s="99"/>
       <c r="AO230" s="14"/>
       <c r="AP230" s="14"/>
       <c r="AQ230" s="15"/>
@@ -32808,10 +32803,10 @@
       <c r="AH231" s="15"/>
       <c r="AI231" s="14"/>
       <c r="AJ231" s="14"/>
-      <c r="AK231" s="117"/>
+      <c r="AK231" s="99"/>
       <c r="AL231" s="14"/>
       <c r="AM231" s="14"/>
-      <c r="AN231" s="117"/>
+      <c r="AN231" s="99"/>
       <c r="AO231" s="14"/>
       <c r="AP231" s="14"/>
       <c r="AQ231" s="15"/>
@@ -32873,10 +32868,10 @@
       <c r="AH232" s="15"/>
       <c r="AI232" s="14"/>
       <c r="AJ232" s="14"/>
-      <c r="AK232" s="117"/>
+      <c r="AK232" s="99"/>
       <c r="AL232" s="14"/>
       <c r="AM232" s="14"/>
-      <c r="AN232" s="117"/>
+      <c r="AN232" s="99"/>
       <c r="AO232" s="14"/>
       <c r="AP232" s="14"/>
       <c r="AQ232" s="15"/>
@@ -33626,17 +33621,17 @@
   <sheetData>
     <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="102" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="E4" s="95" t="s">
+      <c r="C4" s="102"/>
+      <c r="E4" s="110" t="s">
         <v>355</v>
       </c>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="72" t="s">
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="70" t="s">
         <v>284</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -33650,12 +33645,12 @@
       <c r="C5" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="74" t="s">
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72" t="s">
         <v>286</v>
       </c>
-      <c r="H5" s="75" t="s">
+      <c r="H5" s="73" t="s">
         <v>287</v>
       </c>
       <c r="I5" s="24" t="s">
@@ -33712,649 +33707,649 @@
       </c>
     </row>
     <row r="9" spans="2:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E9" s="86" t="s">
+      <c r="E9" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="88"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="105"/>
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E10" s="99" t="s">
+      <c r="E10" s="82" t="s">
         <v>296</v>
       </c>
-      <c r="F10" s="100" t="s">
+      <c r="F10" s="83" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="101" t="s">
+      <c r="G10" s="84" t="s">
         <v>309</v>
       </c>
-      <c r="H10" s="100" t="s">
+      <c r="H10" s="83" t="s">
         <v>310</v>
       </c>
-      <c r="I10" s="102" t="s">
+      <c r="I10" s="85" t="s">
         <v>311</v>
       </c>
-      <c r="J10" s="103" t="s">
+      <c r="J10" s="115" t="s">
         <v>312</v>
       </c>
-      <c r="K10" s="102" t="s">
+      <c r="K10" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="L10" s="104" t="s">
+      <c r="L10" s="86" t="s">
         <v>317</v>
       </c>
-      <c r="M10" s="105" t="s">
+      <c r="M10" s="87" t="s">
         <v>335</v>
       </c>
-      <c r="N10" s="98" t="s">
+      <c r="N10" s="81" t="s">
         <v>334</v>
       </c>
-      <c r="O10" s="110" t="s">
+      <c r="O10" s="92" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="F11" s="79">
-        <v>0</v>
-      </c>
-      <c r="G11" s="80">
-        <v>0</v>
-      </c>
-      <c r="H11" s="79">
+      <c r="F11" s="77">
+        <v>0</v>
+      </c>
+      <c r="G11" s="78">
+        <v>0</v>
+      </c>
+      <c r="H11" s="77">
         <v>48</v>
       </c>
-      <c r="I11" s="80">
+      <c r="I11" s="78">
         <v>48</v>
       </c>
-      <c r="J11" s="81">
-        <v>0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>120</v>
-      </c>
-      <c r="L11" s="83">
+      <c r="J11" s="78">
+        <v>0</v>
+      </c>
+      <c r="K11" s="79">
+        <v>119</v>
+      </c>
+      <c r="L11" s="79">
         <v>5</v>
       </c>
-      <c r="M11" s="83">
-        <v>0</v>
-      </c>
-      <c r="N11" s="106">
+      <c r="M11" s="79">
+        <v>0</v>
+      </c>
+      <c r="N11" s="88">
         <v>110</v>
       </c>
-      <c r="O11" s="109">
+      <c r="O11" s="91">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="F12" s="31">
-        <v>0</v>
-      </c>
-      <c r="G12" s="40">
+      <c r="F12" s="30">
+        <v>0</v>
+      </c>
+      <c r="G12" s="38">
         <v>0</v>
       </c>
       <c r="H12" s="25">
         <v>48</v>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="39">
         <v>48</v>
       </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="32">
-        <v>120</v>
-      </c>
-      <c r="L12" s="37">
+      <c r="J12" s="39">
+        <v>0</v>
+      </c>
+      <c r="K12" s="36">
+        <v>119</v>
+      </c>
+      <c r="L12" s="35">
         <v>5</v>
       </c>
-      <c r="M12" s="38">
-        <v>0</v>
-      </c>
-      <c r="N12" s="107">
+      <c r="M12" s="36">
+        <v>0</v>
+      </c>
+      <c r="N12" s="89">
         <v>110</v>
       </c>
-      <c r="O12" s="37"/>
+      <c r="O12" s="35"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="27" t="s">
         <v>297</v>
       </c>
       <c r="F13" s="25">
         <v>1</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="39">
         <v>230</v>
       </c>
       <c r="H13" s="25">
         <v>48</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="39">
         <v>48</v>
       </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="32">
-        <v>120</v>
-      </c>
-      <c r="L13" s="37">
+      <c r="J13" s="39">
+        <v>0</v>
+      </c>
+      <c r="K13" s="36">
+        <v>119</v>
+      </c>
+      <c r="L13" s="35">
         <v>5</v>
       </c>
-      <c r="M13" s="38">
-        <v>0</v>
-      </c>
-      <c r="N13" s="107">
+      <c r="M13" s="36">
+        <v>0</v>
+      </c>
+      <c r="N13" s="89">
         <v>110</v>
       </c>
-      <c r="O13" s="37"/>
+      <c r="O13" s="35"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="27" t="s">
         <v>298</v>
       </c>
       <c r="F14" s="25">
         <v>1</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="39">
         <v>230</v>
       </c>
       <c r="H14" s="25">
         <v>48</v>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="39">
         <v>48</v>
       </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-      <c r="K14" s="32">
-        <v>120</v>
-      </c>
-      <c r="L14" s="37">
+      <c r="J14" s="39">
+        <v>0</v>
+      </c>
+      <c r="K14" s="36">
+        <v>119</v>
+      </c>
+      <c r="L14" s="35">
         <v>5</v>
       </c>
-      <c r="M14" s="38">
-        <v>0</v>
-      </c>
-      <c r="N14" s="107">
+      <c r="M14" s="36">
+        <v>0</v>
+      </c>
+      <c r="N14" s="89">
         <v>110</v>
       </c>
-      <c r="O14" s="37"/>
+      <c r="O14" s="35"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="27" t="s">
         <v>299</v>
       </c>
       <c r="F15" s="25">
         <v>1</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="39">
         <v>101</v>
       </c>
       <c r="H15" s="25">
         <v>48</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="39">
         <v>48</v>
       </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="32">
-        <v>120</v>
-      </c>
-      <c r="L15" s="37">
+      <c r="J15" s="39">
+        <v>0</v>
+      </c>
+      <c r="K15" s="36">
+        <v>119</v>
+      </c>
+      <c r="L15" s="35">
         <v>5</v>
       </c>
-      <c r="M15" s="38">
-        <v>0</v>
-      </c>
-      <c r="N15" s="107">
+      <c r="M15" s="36">
+        <v>0</v>
+      </c>
+      <c r="N15" s="89">
         <v>110</v>
       </c>
-      <c r="O15" s="37"/>
+      <c r="O15" s="35"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="27" t="s">
         <v>300</v>
       </c>
       <c r="F16" s="25">
         <v>1</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="39">
         <v>230</v>
       </c>
       <c r="H16" s="25">
         <v>48</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="39">
         <v>48</v>
       </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-      <c r="K16" s="32">
-        <v>120</v>
-      </c>
-      <c r="L16" s="37">
+      <c r="J16" s="39">
+        <v>0</v>
+      </c>
+      <c r="K16" s="36">
+        <v>119</v>
+      </c>
+      <c r="L16" s="35">
         <v>5</v>
       </c>
-      <c r="M16" s="38">
-        <v>0</v>
-      </c>
-      <c r="N16" s="107">
+      <c r="M16" s="36">
+        <v>0</v>
+      </c>
+      <c r="N16" s="89">
         <v>110</v>
       </c>
-      <c r="O16" s="37"/>
+      <c r="O16" s="35"/>
     </row>
     <row r="17" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>301</v>
       </c>
       <c r="F17" s="25">
         <v>1</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="39">
         <v>140</v>
       </c>
       <c r="H17" s="25">
         <v>48</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="39">
         <v>48</v>
       </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-      <c r="K17" s="32">
-        <v>120</v>
-      </c>
-      <c r="L17" s="37">
+      <c r="J17" s="39">
+        <v>0</v>
+      </c>
+      <c r="K17" s="36">
+        <v>119</v>
+      </c>
+      <c r="L17" s="35">
         <v>5</v>
       </c>
-      <c r="M17" s="38">
-        <v>0</v>
-      </c>
-      <c r="N17" s="107">
+      <c r="M17" s="36">
+        <v>0</v>
+      </c>
+      <c r="N17" s="89">
         <v>110</v>
       </c>
-      <c r="O17" s="37"/>
+      <c r="O17" s="35"/>
     </row>
     <row r="18" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="27" t="s">
         <v>302</v>
       </c>
       <c r="F18" s="25">
         <v>1</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="39">
         <v>117</v>
       </c>
       <c r="H18" s="25">
         <v>48</v>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="39">
         <v>48</v>
       </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-      <c r="K18" s="32">
-        <v>120</v>
-      </c>
-      <c r="L18" s="37">
+      <c r="J18" s="39">
+        <v>0</v>
+      </c>
+      <c r="K18" s="36">
+        <v>119</v>
+      </c>
+      <c r="L18" s="35">
         <v>5</v>
       </c>
-      <c r="M18" s="38">
-        <v>0</v>
-      </c>
-      <c r="N18" s="107">
+      <c r="M18" s="36">
+        <v>0</v>
+      </c>
+      <c r="N18" s="89">
         <v>110</v>
       </c>
-      <c r="O18" s="37"/>
+      <c r="O18" s="35"/>
     </row>
     <row r="19" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="27" t="s">
         <v>303</v>
       </c>
       <c r="F19" s="25">
         <v>146</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="39">
         <v>146</v>
       </c>
       <c r="H19" s="25">
         <v>48</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="39">
         <v>48</v>
       </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="32">
-        <v>120</v>
-      </c>
-      <c r="L19" s="37">
+      <c r="J19" s="39">
+        <v>0</v>
+      </c>
+      <c r="K19" s="36">
+        <v>119</v>
+      </c>
+      <c r="L19" s="35">
         <v>5</v>
       </c>
-      <c r="M19" s="37">
-        <v>0</v>
-      </c>
-      <c r="N19" s="107">
+      <c r="M19" s="35">
+        <v>0</v>
+      </c>
+      <c r="N19" s="89">
         <v>110</v>
       </c>
-      <c r="O19" s="37"/>
+      <c r="O19" s="35"/>
     </row>
     <row r="20" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="27" t="s">
         <v>304</v>
       </c>
       <c r="F20" s="25">
         <v>178</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="39">
         <v>178</v>
       </c>
       <c r="H20" s="25">
         <v>48</v>
       </c>
-      <c r="I20" s="41">
+      <c r="I20" s="39">
         <v>48</v>
       </c>
-      <c r="J20" s="5">
-        <v>0</v>
-      </c>
-      <c r="K20" s="32">
-        <v>120</v>
-      </c>
-      <c r="L20" s="37">
+      <c r="J20" s="39">
+        <v>0</v>
+      </c>
+      <c r="K20" s="36">
+        <v>119</v>
+      </c>
+      <c r="L20" s="35">
         <v>5</v>
       </c>
-      <c r="M20" s="37">
-        <v>0</v>
-      </c>
-      <c r="N20" s="107">
+      <c r="M20" s="35">
+        <v>0</v>
+      </c>
+      <c r="N20" s="89">
         <v>110</v>
       </c>
-      <c r="O20" s="37"/>
+      <c r="O20" s="35"/>
     </row>
     <row r="21" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="27" t="s">
         <v>305</v>
       </c>
       <c r="F21" s="25">
         <v>1</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="39">
         <v>1</v>
       </c>
       <c r="H21" s="25">
         <v>48</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="39">
         <v>48</v>
       </c>
-      <c r="J21" s="5">
-        <v>0</v>
-      </c>
-      <c r="K21" s="32">
-        <v>120</v>
-      </c>
-      <c r="L21" s="37">
+      <c r="J21" s="39">
+        <v>0</v>
+      </c>
+      <c r="K21" s="36">
+        <v>119</v>
+      </c>
+      <c r="L21" s="35">
         <v>5</v>
       </c>
-      <c r="M21" s="37">
-        <v>0</v>
-      </c>
-      <c r="N21" s="107">
+      <c r="M21" s="35">
+        <v>0</v>
+      </c>
+      <c r="N21" s="89">
         <v>110</v>
       </c>
-      <c r="O21" s="37"/>
+      <c r="O21" s="35"/>
     </row>
     <row r="22" spans="5:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="27" t="s">
         <v>306</v>
       </c>
       <c r="F22" s="25">
         <v>160</v>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="39">
         <v>160</v>
       </c>
       <c r="H22" s="25">
         <v>48</v>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="39">
         <v>48</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="39">
         <v>-20</v>
       </c>
-      <c r="K22" s="32">
-        <v>120</v>
-      </c>
-      <c r="L22" s="37">
+      <c r="K22" s="36">
+        <v>119</v>
+      </c>
+      <c r="L22" s="35">
         <v>5</v>
       </c>
-      <c r="M22" s="37">
+      <c r="M22" s="35">
         <v>-20</v>
       </c>
-      <c r="N22" s="107">
+      <c r="N22" s="89">
         <v>110</v>
       </c>
-      <c r="O22" s="37">
+      <c r="O22" s="35">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="28" t="s">
         <v>307</v>
       </c>
       <c r="F23" s="26">
         <v>210</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="40">
         <v>210</v>
       </c>
       <c r="H23" s="26">
         <v>48</v>
       </c>
-      <c r="I23" s="42">
+      <c r="I23" s="40">
         <v>48</v>
       </c>
-      <c r="J23" s="52">
+      <c r="J23" s="40">
         <v>-20</v>
       </c>
-      <c r="K23" s="27">
-        <v>120</v>
-      </c>
-      <c r="L23" s="34">
+      <c r="K23" s="116">
+        <v>119</v>
+      </c>
+      <c r="L23" s="32">
         <v>5</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="32">
         <v>-20</v>
       </c>
-      <c r="N23" s="108">
+      <c r="N23" s="90">
         <v>110</v>
       </c>
-      <c r="O23" s="34">
-        <v>15</v>
+      <c r="O23" s="32">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="5:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E26" s="86" t="s">
+      <c r="E26" s="103" t="s">
         <v>325</v>
       </c>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="88"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="104"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="105"/>
     </row>
     <row r="27" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E27" s="89" t="s">
+      <c r="E27" s="106" t="s">
         <v>326</v>
       </c>
-      <c r="F27" s="90"/>
-      <c r="G27" s="77" t="s">
+      <c r="F27" s="107"/>
+      <c r="G27" s="75" t="s">
         <v>318</v>
       </c>
-      <c r="H27" s="33" t="s">
+      <c r="H27" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="I27" s="33" t="s">
+      <c r="I27" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="J27" s="33" t="s">
+      <c r="J27" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="K27" s="33" t="s">
+      <c r="K27" s="31" t="s">
         <v>327</v>
       </c>
-      <c r="L27" s="33" t="s">
+      <c r="L27" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="M27" s="33" t="s">
+      <c r="M27" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="N27" s="35" t="s">
+      <c r="N27" s="33" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="28" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E28" s="91"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="34">
-        <v>2.5</v>
-      </c>
-      <c r="H28" s="34">
+      <c r="E28" s="108"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="32">
+        <v>2.5</v>
+      </c>
+      <c r="H28" s="32">
         <v>4.97</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="32">
         <v>5.0199999999999996</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="32">
         <v>4.97</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="32">
         <v>5.0199999999999996</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="32">
         <v>100000</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="32">
         <v>4.9400000000000004</v>
       </c>
-      <c r="N28" s="36">
+      <c r="N28" s="34">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="5:15" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E31" s="86" t="s">
+      <c r="E31" s="103" t="s">
         <v>314</v>
       </c>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="94"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="114"/>
     </row>
     <row r="32" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="F32" s="46" t="s">
+      <c r="F32" s="44" t="s">
         <v>308</v>
       </c>
-      <c r="G32" s="47" t="s">
+      <c r="G32" s="45" t="s">
         <v>309</v>
       </c>
-      <c r="H32" s="46" t="s">
+      <c r="H32" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="I32" s="48" t="s">
+      <c r="I32" s="46" t="s">
         <v>311</v>
       </c>
-      <c r="J32" s="44" t="s">
+      <c r="J32" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="K32" s="48" t="s">
+      <c r="K32" s="46" t="s">
         <v>313</v>
       </c>
-      <c r="L32" s="49" t="s">
+      <c r="L32" s="47" t="s">
         <v>317</v>
       </c>
-      <c r="M32" s="50" t="s">
+      <c r="M32" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="N32" s="50" t="s">
+      <c r="N32" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="O32" s="49" t="s">
+      <c r="O32" s="47" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="33" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E33" s="111" t="s">
+      <c r="E33" s="93" t="s">
         <v>356</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="49">
         <v>80</v>
       </c>
-      <c r="G33" s="51">
+      <c r="G33" s="49">
         <v>80</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="49">
         <v>48</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="49">
         <v>48</v>
       </c>
-      <c r="J33" s="51">
-        <v>0</v>
-      </c>
-      <c r="K33" s="51">
+      <c r="J33" s="49">
+        <v>0</v>
+      </c>
+      <c r="K33" s="49">
         <v>140</v>
       </c>
-      <c r="L33" s="51">
+      <c r="L33" s="49">
         <v>5</v>
       </c>
-      <c r="M33" s="51">
-        <v>0</v>
-      </c>
-      <c r="N33" s="51">
+      <c r="M33" s="49">
+        <v>0</v>
+      </c>
+      <c r="N33" s="49">
         <v>110</v>
       </c>
-      <c r="O33" s="112"/>
+      <c r="O33" s="94"/>
     </row>
     <row r="34" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E34" s="113" t="s">
+      <c r="E34" s="95" t="s">
         <v>357</v>
       </c>
       <c r="F34" s="5">
@@ -34384,10 +34379,10 @@
       <c r="N34" s="5">
         <v>110</v>
       </c>
-      <c r="O34" s="114"/>
+      <c r="O34" s="96"/>
     </row>
     <row r="35" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E35" s="113" t="s">
+      <c r="E35" s="95" t="s">
         <v>350</v>
       </c>
       <c r="F35" s="5">
@@ -34417,10 +34412,10 @@
       <c r="N35" s="5">
         <v>110</v>
       </c>
-      <c r="O35" s="114"/>
+      <c r="O35" s="96"/>
     </row>
     <row r="36" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="E36" s="113" t="s">
+      <c r="E36" s="95" t="s">
         <v>351</v>
       </c>
       <c r="F36" s="5">
@@ -34450,52 +34445,52 @@
       <c r="N36" s="5">
         <v>110</v>
       </c>
-      <c r="O36" s="114"/>
+      <c r="O36" s="96"/>
     </row>
     <row r="37" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E37" s="115" t="s">
+      <c r="E37" s="97" t="s">
         <v>352</v>
       </c>
-      <c r="F37" s="52">
+      <c r="F37" s="50">
         <v>2</v>
       </c>
-      <c r="G37" s="52">
+      <c r="G37" s="50">
         <v>133</v>
       </c>
-      <c r="H37" s="52">
+      <c r="H37" s="50">
         <v>48</v>
       </c>
-      <c r="I37" s="52">
+      <c r="I37" s="50">
         <v>48</v>
       </c>
-      <c r="J37" s="52">
-        <v>0</v>
-      </c>
-      <c r="K37" s="52">
+      <c r="J37" s="50">
+        <v>0</v>
+      </c>
+      <c r="K37" s="50">
         <v>140</v>
       </c>
-      <c r="L37" s="52">
+      <c r="L37" s="50">
         <v>5</v>
       </c>
-      <c r="M37" s="52">
-        <v>0</v>
-      </c>
-      <c r="N37" s="52">
+      <c r="M37" s="50">
+        <v>0</v>
+      </c>
+      <c r="N37" s="50">
         <v>110</v>
       </c>
-      <c r="O37" s="116"/>
+      <c r="O37" s="98"/>
     </row>
     <row r="42" spans="5:15" x14ac:dyDescent="0.3">
-      <c r="G42" s="76"/>
+      <c r="G42" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="E31:O31"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E26:N26"/>
     <mergeCell ref="E27:F28"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="E9:O9"/>
-    <mergeCell ref="E31:O31"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34504,31 +34499,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="50a08be1-ba3e-4a79-8f58-48006bbce96a" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949" xsi:nil="true"/>
-    <State xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949">New</State>
-    <TaxKeywordTaxHTField xmlns="50a08be1-ba3e-4a79-8f58-48006bbce96a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007EAF870E99ECA94F864B327C5B7E3838" ma:contentTypeVersion="31" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="395773d36c2f521a29f182556c34a191">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="04cfd3d3-2c89-4764-aaab-c87677d64949" xmlns:ns3="448318fe-d517-4740-9c4f-0b0645b4226a" xmlns:ns4="50a08be1-ba3e-4a79-8f58-48006bbce96a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fa62a5032f3abd9d41835b1ea6091fec" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="04cfd3d3-2c89-4764-aaab-c87677d64949"/>
@@ -34814,10 +34784,47 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="50a08be1-ba3e-4a79-8f58-48006bbce96a" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949" xsi:nil="true"/>
+    <State xmlns="04cfd3d3-2c89-4764-aaab-c87677d64949">New</State>
+    <TaxKeywordTaxHTField xmlns="50a08be1-ba3e-4a79-8f58-48006bbce96a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFA3AA9-6430-449F-9930-F36527A7FEB5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6E5232F-F37E-427A-A8C4-17F8B14F4745}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="04cfd3d3-2c89-4764-aaab-c87677d64949"/>
+    <ds:schemaRef ds:uri="448318fe-d517-4740-9c4f-0b0645b4226a"/>
+    <ds:schemaRef ds:uri="50a08be1-ba3e-4a79-8f58-48006bbce96a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34841,21 +34848,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6E5232F-F37E-427A-A8C4-17F8B14F4745}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFA3AA9-6430-449F-9930-F36527A7FEB5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="04cfd3d3-2c89-4764-aaab-c87677d64949"/>
-    <ds:schemaRef ds:uri="448318fe-d517-4740-9c4f-0b0645b4226a"/>
-    <ds:schemaRef ds:uri="50a08be1-ba3e-4a79-8f58-48006bbce96a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
